--- a/output/full_scan/batch_seq0_2026-10-08.xlsx
+++ b/output/full_scan/batch_seq0_2026-10-08.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O113"/>
+  <dimension ref="A1:O114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>68.75088630983015</v>
+        <v>68.75088630194595</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>28.10480803434653</v>
+        <v>28.10480802837484</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>3.116797984523913</v>
@@ -570,7 +570,7 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>2.323663420323658</v>
+        <v>2.32366342052393</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>78.06529999465224</v>
+        <v>78.06529998048428</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>29.723726801686</v>
@@ -623,7 +623,7 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.4992150977427323</v>
+        <v>0.4992150978206189</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>81.79201382553688</v>
+        <v>81.79201383293488</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>26.23343327061948</v>
+        <v>26.23343329350317</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>5.050581260309642</v>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>68.88225653755634</v>
+        <v>68.88225610974031</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>12.71477366007274</v>
+        <v>12.71477370009238</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>6.053438558221076</v>
@@ -729,7 +729,7 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1809120753125356</v>
+        <v>0.1809120752235085</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>58.45018457149006</v>
+        <v>58.45018457873667</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>20.14320843719862</v>
+        <v>20.14320843718718</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>2.708240513887385</v>
@@ -782,7 +782,7 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>2.546725260468336</v>
+        <v>2.546725260635307</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>65.4924712731695</v>
+        <v>65.49247125176757</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>29.36609390740152</v>
+        <v>29.36609422556742</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>3.527633586080116</v>
@@ -835,7 +835,7 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1320563078760441</v>
+        <v>0.1320563081430936</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -870,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>76.849382813411</v>
+        <v>76.84938281567884</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>31.90821659403513</v>
+        <v>31.90821670864898</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>3.499430075610211</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>62.6360046684589</v>
+        <v>62.63600458498946</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>15.35174302840022</v>
+        <v>15.35174302150767</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>1.11718406970062</v>
@@ -941,7 +941,7 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.2909560717792241</v>
+        <v>0.2909560719683808</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>68.18608200837757</v>
+        <v>68.18608195405631</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>20.83721268174775</v>
+        <v>20.83721276025852</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>2.057571107754822</v>
@@ -994,7 +994,7 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.1903219130132539</v>
+        <v>0.1903219129909951</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1029,10 +1029,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>70.13349677762514</v>
+        <v>70.13349679223855</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>28.70745280307643</v>
+        <v>28.70745281351844</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>0.4778863829004696</v>
@@ -1047,7 +1047,7 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>34.0466190789693</v>
+        <v>34.04661907863557</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>72.94163909313119</v>
+        <v>72.94163909775374</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>41.41361471527915</v>
+        <v>41.41361485522605</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>0.6692625531607514</v>
@@ -1100,7 +1100,7 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>2.775680817640032</v>
+        <v>2.775680817539896</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>63.96691402969447</v>
+        <v>63.96691404230935</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>25.18102127275927</v>
+        <v>25.18102129205635</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>1.963357044455915</v>
@@ -1153,7 +1153,7 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.5732859228292085</v>
+        <v>0.5732859227846997</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>81.41370497450623</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>19.53505082745521</v>
+        <v>19.53505082383182</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>6.473611031608359</v>
@@ -1206,7 +1206,7 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.0805967524701133</v>
+        <v>0.08059675246788819</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>59.49662282764354</v>
+        <v>59.49662286232611</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>14.91323106520272</v>
+        <v>14.91323117272427</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>1.534705958997361</v>
@@ -1259,7 +1259,7 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>1.81658838943619</v>
+        <v>1.816588389102366</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1294,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>62.43889722869301</v>
+        <v>62.4388972160024</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>23.22194566146313</v>
+        <v>23.22194564865272</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>2.458606094843628</v>
@@ -1312,7 +1312,7 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.3632003323228847</v>
+        <v>0.3632003323340169</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>70.71997508252586</v>
+        <v>70.71997515412083</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>40.20627996252343</v>
+        <v>40.20627999984774</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>1.046727163758227</v>
@@ -1365,7 +1365,7 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>1.493546112451403</v>
+        <v>1.493546111939554</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>67.49986163515482</v>
+        <v>67.49986155495134</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>21.69462928795211</v>
+        <v>21.69462928795212</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>0.7143601124408506</v>
@@ -1418,7 +1418,7 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.0759083796353363</v>
+        <v>0.07590837969097181</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>777.3658025572967</v>
+        <v>777.3658025572961</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>36.2</v>
@@ -1453,10 +1453,10 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>65.64095186614063</v>
+        <v>65.64095183501165</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>31.89755909371357</v>
+        <v>31.89755916350121</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>2.945092476757206</v>
@@ -1471,7 +1471,7 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.3817856751179609</v>
+        <v>0.3817856753405028</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1506,10 +1506,10 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>64.16993953618621</v>
+        <v>64.16993954706138</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>20.51075578363416</v>
+        <v>20.51075583973391</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>2.027136419647595</v>
@@ -1545,7 +1545,7 @@
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>722.0710344939586</v>
+        <v>722.0710344939591</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>57.1</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>61.87037163878394</v>
+        <v>61.87037167701789</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>23.265641991507</v>
+        <v>23.26564229588845</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>0.7971046390887576</v>
@@ -1577,7 +1577,7 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.4582647861642449</v>
+        <v>0.4582647886122225</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>54.63505013526317</v>
+        <v>54.63505011888225</v>
       </c>
       <c r="I22" s="2" t="n">
         <v>5.317508232370102</v>
@@ -1630,7 +1630,7 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.1002464076346131</v>
+        <v>0.1002464076301624</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>59.57192611220072</v>
+        <v>59.57192608557797</v>
       </c>
       <c r="I23" s="2" t="n">
         <v>15.09701592889266</v>
@@ -1718,7 +1718,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>57.41382265189177</v>
+        <v>57.41382261893338</v>
       </c>
       <c r="I24" s="2" t="n">
         <v>21.01761265133142</v>
@@ -1771,10 +1771,10 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>68.28773730347979</v>
+        <v>68.28773730178901</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>15.89479291596174</v>
+        <v>15.8947929021889</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>2.922459904062402</v>
@@ -1789,7 +1789,7 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.8632536762476652</v>
+        <v>0.863253676281051</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>626.8801999860289</v>
+        <v>626.8801999860286</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>54.5</v>
@@ -1824,10 +1824,10 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>55.20473612033051</v>
+        <v>55.20473590781823</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>37.57523368512677</v>
+        <v>37.57523380679167</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>0.2622878238583767</v>
@@ -1842,7 +1842,7 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.0543360411622253</v>
+        <v>-0.0543360403054329</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>47.78381084363092</v>
+        <v>47.78381090987602</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>12.59873217536886</v>
+        <v>12.5987322285307</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>0.6813679857092976</v>
@@ -1895,7 +1895,7 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-6.808955179856783</v>
+        <v>-6.808955191873824</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1930,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>49.11929431432637</v>
+        <v>49.11929440422172</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>19.00406645332382</v>
+        <v>19.00406645416426</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>2.064014355832512</v>
@@ -1948,7 +1948,7 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.3928557140660749</v>
+        <v>0.3928557141328472</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1983,10 +1983,10 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>54.47009010002702</v>
+        <v>54.47009015855016</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>38.52500912932713</v>
+        <v>38.52500912334865</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>0.2039126708344463</v>
@@ -2001,7 +2001,7 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.0536524988879631</v>
+        <v>-0.0536524989102179</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>592.9609450057661</v>
+        <v>592.9609450057658</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>50.1</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>55.83981792889423</v>
+        <v>55.83982313956914</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>4.15883437011667</v>
+        <v>4.15883751812657</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>0.3131403187712136</v>
@@ -2054,7 +2054,7 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.1419729153887863</v>
+        <v>0.1419729024590614</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2089,10 +2089,10 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>55.07556763720398</v>
+        <v>55.07556762034065</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>23.30970629242926</v>
+        <v>23.30970629242927</v>
       </c>
       <c r="J31" s="2" t="n">
         <v>0.1556558365170188</v>
@@ -2107,7 +2107,7 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.8245204240120145</v>
+        <v>-0.8245204238784813</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>580.6920907104045</v>
+        <v>580.6920907104044</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>19.4</v>
@@ -2142,10 +2142,10 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>58.9885069063583</v>
+        <v>58.98850584969143</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>28.83387742313903</v>
+        <v>28.8338775140695</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>0.5116185890333</v>
@@ -2160,7 +2160,7 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.036732341266239</v>
+        <v>0.0367323419004866</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>573.2361473756251</v>
+        <v>573.2361473756329</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>56.5</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>58.7480753032942</v>
+        <v>58.74807538178406</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>22.86551432278713</v>
+        <v>22.86551436745738</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>1.108350446873547</v>
@@ -2213,7 +2213,7 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.9196934811531025</v>
+        <v>0.9196934811197246</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>561.6707711957355</v>
+        <v>561.6707711957353</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>326.5</v>
@@ -2248,10 +2248,10 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>48.7561672016767</v>
+        <v>48.75616725156184</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>12.04954643535327</v>
+        <v>12.04954635460285</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>0.6845297377637236</v>
@@ -2266,7 +2266,7 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.2254880770439515</v>
+        <v>0.2254880767101654</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>555.3485885976602</v>
+        <v>555.3485885976603</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>8.630000000000001</v>
@@ -2301,10 +2301,10 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>53.37589170739363</v>
+        <v>53.37589158422116</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>19.95622739250248</v>
+        <v>19.95622744640882</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>1.06436812333298</v>
@@ -2319,7 +2319,7 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.0257830548358856</v>
+        <v>0.0257830548826195</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>53.29672525409468</v>
+        <v>53.29672523006876</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>27.90689907563864</v>
+        <v>27.9068990583525</v>
       </c>
       <c r="J36" s="2" t="n">
         <v>0.5209096159834906</v>
@@ -2372,7 +2372,7 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.2432142379899655</v>
+        <v>0.2432142382569972</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>47.11262054916919</v>
+        <v>47.11262062905258</v>
       </c>
       <c r="I37" s="2" t="n">
         <v>10.34898960042178</v>
@@ -2425,7 +2425,7 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.7176654356752254</v>
+        <v>-0.717665441127562</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2460,10 +2460,10 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>54.5972931428327</v>
+        <v>54.59729309788906</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>28.03695150926717</v>
+        <v>28.0369515793599</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>0.3314914356505022</v>
@@ -2478,7 +2478,7 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-0.1768901606097204</v>
+        <v>-0.1768901601868906</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>57.70629572668711</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>28.15750572574126</v>
+        <v>28.15750577498932</v>
       </c>
       <c r="J39" s="2" t="n">
         <v>0.4782481924665126</v>
@@ -2531,7 +2531,7 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.1912227347905357</v>
+        <v>0.1912227348127948</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2566,10 +2566,10 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>64.76987250171476</v>
+        <v>64.76987253322193</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>32.53685417157057</v>
+        <v>32.53685413188181</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>0.5670663761275974</v>
@@ -2594,21 +2594,21 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>8050</v>
+        <v>8227</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>廣積</t>
+          <t>巨有科技</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>521.7783768168604</v>
+        <v>523.0926847156088</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>60.4</v>
+        <v>335</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>52.38533298413126</v>
+        <v>65.40637199469262</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>27.28451893778002</v>
+        <v>49.07272363073445</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.5146268722717706</v>
+        <v>0.3507565649380665</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.0012711431966812</v>
+        <v>1.505232419359622</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>9955</v>
+        <v>8050</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>佳龍</t>
+          <t>廣積</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>515.1378922641562</v>
+        <v>521.7783768168604</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>24.1</v>
+        <v>60.4</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>56.83079493831094</v>
+        <v>52.38533300237361</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>13.91453302642374</v>
+        <v>27.28451893778002</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>2.392350724340234</v>
+        <v>0.5146268722717706</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.1424846873850181</v>
+        <v>0.0012711431299166</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>8093</v>
+        <v>9955</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>保銳</t>
+          <t>佳龍</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>510.8726056327984</v>
+        <v>515.1378922641563</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>26.3</v>
+        <v>24.1</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>54.20933335876976</v>
+        <v>56.830794914371</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>12.7852258228285</v>
+        <v>13.91453306425982</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.171671703038444</v>
+        <v>2.392350724340234</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>1</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.2205070165157744</v>
+        <v>0.1424846873738943</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>8103</v>
+        <v>8093</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>瀚荃</t>
+          <t>保銳</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>470.3182288805356</v>
+        <v>510.8726056327984</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>114.5</v>
+        <v>26.3</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>47.65076333428527</v>
+        <v>54.20933332074446</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>34.00702984946201</v>
+        <v>12.78522607080232</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.3792983774624572</v>
+        <v>1.171671703038444</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-1.895591269601346</v>
+        <v>0.220507016725546</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>8431</v>
+        <v>8103</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>匯鑽科</t>
+          <t>瀚荃</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>466.6384434013606</v>
+        <v>470.3182288805356</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>59.6</v>
+        <v>114.5</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>47.42181606569423</v>
+        <v>47.65076332000302</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>30.89764323758262</v>
+        <v>34.00702985134878</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.8821235310731542</v>
+        <v>0.3792983774624572</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.8736886220083897</v>
+        <v>-1.895591269792043</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>8054</v>
+        <v>8431</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>安國</t>
+          <t>匯鑽科</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>461.0112710596544</v>
+        <v>466.6384434013606</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>81</v>
+        <v>59.6</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>40.58445089022686</v>
+        <v>47.42181609444074</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>22.4832176945309</v>
+        <v>30.8976432166122</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.5953315198623444</v>
+        <v>0.8821235310731542</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.3258135901046283</v>
+        <v>-0.8736886222309268</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>8234</v>
+        <v>8054</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>新漢</t>
+          <t>安國</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>460.538957417092</v>
+        <v>461.0112710596544</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>63.4</v>
+        <v>81</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>49.26418367201131</v>
+        <v>40.58445084506695</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>17.75820008443963</v>
+        <v>22.48321764170405</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.565331861728069</v>
+        <v>0.5953315198623444</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.2312142095599967</v>
+        <v>-0.3258135906609768</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>8467</v>
+        <v>8234</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>波力-KY</t>
+          <t>新漢</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>458.3304688996724</v>
+        <v>460.538957417092</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>90.7</v>
+        <v>63.4</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>51.24182341014726</v>
+        <v>49.26418390999588</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>7.409446058844594</v>
+        <v>17.75820008719286</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.4348522983750438</v>
+        <v>1.565331861728069</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.8011644506100102</v>
+        <v>0.2312142095599967</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>8932</v>
+        <v>8467</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>智通*</t>
+          <t>波力-KY</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>456.8992214466853</v>
+        <v>458.3304688996722</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>92.7</v>
+        <v>90.7</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>47.85265624441858</v>
+        <v>51.24182341014726</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>16.90142861533962</v>
+        <v>7.409446058844591</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.207241727081338</v>
+        <v>0.4348522983750438</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.4152180222925548</v>
+        <v>0.8011644501649202</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>8102</v>
+        <v>8932</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>傑霖科技</t>
+          <t>智通*</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>455.7379059819353</v>
+        <v>456.8992214466853</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>60.5</v>
+        <v>92.7</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>51.09471768936334</v>
+        <v>47.85265698818198</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>5.215469000058436</v>
+        <v>16.90142867001112</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.061167350748045</v>
+        <v>1.207241727081338</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>1.315487352606058</v>
+        <v>0.4152180221018553</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>8410</v>
+        <v>8102</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>森田</t>
+          <t>傑霖科技</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>453.3787349832285</v>
+        <v>455.7379059819353</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>26.45</v>
+        <v>60.5</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>19.97018301705707</v>
+        <v>51.09471769887392</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>49.0428579757434</v>
+        <v>5.215468956324937</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.606984700735965</v>
+        <v>1.061167350748045</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.1275823390345335</v>
+        <v>1.315487352717326</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>8121</v>
+        <v>8410</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>越峰</t>
+          <t>森田</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>447.0431000301944</v>
+        <v>453.378734983228</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>34.4</v>
+        <v>26.45</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>65.56629660862872</v>
+        <v>19.97018239934931</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>33.144284573052</v>
+        <v>49.04285851443795</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>2.228843037556953</v>
+        <v>1.606984700735965</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.6710381744579674</v>
+        <v>-0.1275823386673414</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>8070</v>
+        <v>8121</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>越峰</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>439.2716921379515</v>
+        <v>447.0431000301944</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>50.5</v>
+        <v>34.4</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,49 +3255,49 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>51.64396861968283</v>
+        <v>65.5662966628927</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>17.9507663714873</v>
+        <v>33.14428458119747</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.261462616369482</v>
+        <v>2.228843037556953</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.1092348925514607</v>
+        <v>0.6710381744245847</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>8383</v>
+        <v>8070</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>千附</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>432.7185481448347</v>
+        <v>439.2716921379535</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>69</v>
+        <v>50.5</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,25 +3308,25 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>53.70635723238732</v>
+        <v>51.64396867004989</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>18.66799540122203</v>
+        <v>17.95076643234812</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.7225547931200471</v>
+        <v>1.261462616369482</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.4690026350815705</v>
+        <v>0.1092348924513225</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -3336,21 +3336,21 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>8059</v>
+        <v>8383</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>凱碩</t>
+          <t>千附</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>424.7820793364625</v>
+        <v>432.7185481448347</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>17.6</v>
+        <v>69</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>60.25695106630395</v>
+        <v>53.70635728600141</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>27.2311605372665</v>
+        <v>18.66799548297174</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.24034330025339</v>
+        <v>0.7225547931200471</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.1234104532535235</v>
+        <v>0.4690026349035413</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>8072</v>
+        <v>8059</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>陞泰</t>
+          <t>凱碩</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>420.468522814218</v>
+        <v>424.7820793364625</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>26.9</v>
+        <v>17.6</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>48.05622872967945</v>
+        <v>60.25695172624757</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>36.87661596134209</v>
+        <v>27.2311602706</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.4191745087014877</v>
+        <v>0.24034330025339</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.0617997257569833</v>
+        <v>0.1234104521283996</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>8147</v>
+        <v>8072</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>正淩</t>
+          <t>陞泰</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>414.2031695476913</v>
+        <v>420.468522814218</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>139</v>
+        <v>26.9</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>52.08418880009766</v>
+        <v>48.05622873834169</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>31.04128222347408</v>
+        <v>36.87661600599267</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.432183151738959</v>
+        <v>0.4191745087014877</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.2512553512628273</v>
+        <v>-0.0617997258459984</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>8104</v>
+        <v>8147</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>錸寶</t>
+          <t>正淩</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>410.3640017409335</v>
+        <v>414.2031695476912</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>30.95</v>
+        <v>139</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>48.5751410617034</v>
+        <v>52.08418875083346</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>16.00618361124459</v>
+        <v>31.04128221608954</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.6734366827199414</v>
+        <v>0.432183151738959</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.08240260635907259</v>
+        <v>-0.2512553510402679</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>8096</v>
+        <v>8104</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>錸寶</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>404.2055890913488</v>
+        <v>410.3640017409354</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>90.3</v>
+        <v>30.95</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>41.87255006573863</v>
+        <v>48.57514128544108</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>31.70957461096691</v>
+        <v>16.00618360180705</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.5161376373223423</v>
+        <v>0.6734366827199414</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>1.538462846467473</v>
+        <v>0.082402606448088</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>8092</v>
+        <v>8096</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>建暐</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>403.2234296852503</v>
+        <v>404.2055890913488</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>12.75</v>
+        <v>90.3</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>51.66410358057581</v>
+        <v>41.87255004124982</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>13.64569299449126</v>
+        <v>31.70957464210655</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>3.650182642688881</v>
+        <v>0.5161376373223423</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.0167549748437294</v>
+        <v>1.538462846434086</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>8277</v>
+        <v>8092</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>商丞</t>
+          <t>建暐</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>401.2868373581584</v>
+        <v>403.2234296852506</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>15.45</v>
+        <v>12.75</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>78.68008854393071</v>
+        <v>51.66410364899698</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>37.30805680446469</v>
+        <v>13.64569296770591</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.1808425508974529</v>
+        <v>3.650182642688881</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.1343239081506677</v>
+        <v>-0.016754974943874</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>8423</v>
+        <v>8277</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>保綠-KY</t>
+          <t>商丞</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>398.9345315449172</v>
+        <v>401.2868373581581</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>17.8</v>
+        <v>15.45</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>44.94763310617085</v>
+        <v>78.68008853777276</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>20.60234965574371</v>
+        <v>37.30805682429794</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.6610502872841946</v>
+        <v>0.1808425508974529</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.0228012556472993</v>
+        <v>0.1343239081888085</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>8473</v>
+        <v>8423</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>山林水</t>
+          <t>保綠-KY</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>396.848020265179</v>
+        <v>398.9345315449172</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>39.8</v>
+        <v>17.8</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>44.64499191450182</v>
+        <v>44.94763305541719</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>21.3913657421038</v>
+        <v>20.60234961324448</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.5692080331342624</v>
+        <v>0.6610502872841946</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,7 +3803,7 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.3123991655835492</v>
+        <v>-0.0228012556361702</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -3813,41 +3813,41 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>8183</v>
+        <v>8473</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>精星</t>
+          <t>山林水</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>395.8634049635208</v>
+        <v>396.8480202651788</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>28.2</v>
+        <v>39.8</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G64" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>44.9026885539789</v>
+        <v>44.64499201724888</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>19.14537614643788</v>
+        <v>21.39136576494574</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.870816255095116</v>
+        <v>0.5692080331342624</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,48 +3856,48 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.0686206106538616</v>
+        <v>0.3123991656391873</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>8210</v>
+        <v>8183</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>精星</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>389.1256232099181</v>
+        <v>395.8634049635209</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>874</v>
+        <v>28.2</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G65" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>42.30937046793932</v>
+        <v>44.90268834399803</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>18.98298201389076</v>
+        <v>19.1453761405531</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.9402414291795336</v>
+        <v>1.870816255095116</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>5.455581065319805</v>
+        <v>0.068620610797997</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>8499</v>
+        <v>8210</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>鼎炫-KY</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>385.4744141746591</v>
+        <v>389.1256232099181</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>253.5</v>
+        <v>874</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>50.8539070820677</v>
+        <v>42.30937054187002</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>8.512516487661596</v>
+        <v>18.9829820197608</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.3401844706912896</v>
+        <v>0.9402414291795336</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>2.469308959111592</v>
+        <v>5.455581065764903</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>8440</v>
+        <v>8499</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>綠電</t>
+          <t>鼎炫-KY</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>381.883635821929</v>
+        <v>385.4744141746589</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>20.1</v>
+        <v>253.5</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>48.47937294028981</v>
+        <v>50.85390714794104</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>18.18963205341544</v>
+        <v>8.51251650267225</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.5895896159336576</v>
+        <v>0.3401844706912896</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,7 +4015,7 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.0076392896758236</v>
+        <v>2.469308960224295</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
@@ -4025,21 +4025,21 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>8462</v>
+        <v>8440</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>柏文</t>
+          <t>綠電</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>373.6262227857153</v>
+        <v>381.883635821929</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>156</v>
+        <v>20.1</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>37.31450994201786</v>
+        <v>48.47937300937726</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>32.27104996700624</v>
+        <v>18.189632038254</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>2.027341329392833</v>
+        <v>0.5895896159336576</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.06564547922579141</v>
+        <v>-0.0076392896313175</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>8069</v>
+        <v>8462</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>元太</t>
+          <t>柏文</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>368.4434208113037</v>
+        <v>373.6262227857153</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,49 +4103,49 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>40.36133811312454</v>
+        <v>37.31450991342541</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>27.16716233292931</v>
+        <v>32.27104997860098</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.5989563875292683</v>
+        <v>2.027341329392833</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L69" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>1.113482671417484</v>
+        <v>-0.06564547922579141</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>8477</v>
+        <v>8069</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>創業家</t>
+          <t>元太</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>363.8756244375477</v>
+        <v>368.4434208113037</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>13.5</v>
+        <v>144</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,49 +4156,49 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>28.91138073460135</v>
+        <v>40.36133842359701</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>27.43463917078544</v>
+        <v>27.1671622292828</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>3.017999211374759</v>
+        <v>0.5989563875292683</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.0719912016184712</v>
+        <v>1.113482669414593</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>8488</v>
+        <v>8477</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>吉源-KY</t>
+          <t>創業家</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>347.4869459581391</v>
+        <v>363.8756244375477</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>8.18684954284987</v>
+        <v>28.91138071499005</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>38.91875935238748</v>
+        <v>27.43463926876743</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0</v>
+        <v>3.017999211374759</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,28 +4227,28 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.6442186113539309</v>
+        <v>-0.07199120157396439</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>8455</v>
+        <v>8488</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>大拓-KY</t>
+          <t>吉源-KY</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>342.2541318927297</v>
+        <v>347.4869459581391</v>
       </c>
       <c r="E72" s="2" t="n">
         <v>0</v>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>37.93765132692744</v>
+        <v>8.186849530617351</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>10.2919145562585</v>
+        <v>38.91875935043327</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.1481788815458021</v>
+        <v>0</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-1.025581048474408</v>
+        <v>-0.6442186113205489</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>8105</v>
+        <v>8455</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>凌巨</t>
+          <t>大拓-KY</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>341.3092678897987</v>
+        <v>342.2541318927333</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>46.36827811536136</v>
+        <v>37.93765132727655</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>19.82358683737959</v>
+        <v>10.29191459269391</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.6231276079596844</v>
+        <v>0.1481788815458021</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.0809486698689951</v>
+        <v>-1.025581048485533</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>8466</v>
+        <v>8105</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>美吉吉-KY</t>
+          <t>凌巨</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>339.6344894061997</v>
+        <v>341.3092678897987</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>15.05</v>
+        <v>15</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>47.36883120079964</v>
+        <v>46.36827816468684</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>25.76774562942403</v>
+        <v>19.82358684480572</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.4300255712662324</v>
+        <v>0.6231276079596844</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.070435858047665</v>
+        <v>0.08094866985133729</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>8048</v>
+        <v>8466</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>德勝</t>
+          <t>美吉吉-KY</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>328.0107544953105</v>
+        <v>339.6344894061998</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>51.4</v>
+        <v>15.05</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>54.45463921433294</v>
+        <v>47.36883121178813</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>12.934393936509</v>
+        <v>25.76774569806857</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.8082742977947626</v>
+        <v>0.4300255712662324</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.3510327509821866</v>
+        <v>0.0704358580365383</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>8076</v>
+        <v>8048</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>伍豐</t>
+          <t>德勝</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>325.5823637249029</v>
+        <v>328.0107544953105</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>21.4</v>
+        <v>51.4</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>40.96968359849118</v>
+        <v>54.4546393564756</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>21.6669384656097</v>
+        <v>12.93439385840971</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.6812827466472959</v>
+        <v>0.8082742977947626</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.0514943742334104</v>
+        <v>0.3510327509488143</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>8463</v>
+        <v>8076</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>潤泰材</t>
+          <t>伍豐</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>320.9511533058238</v>
+        <v>325.5823637249029</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>49.5099285369536</v>
+        <v>40.96968395903292</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>26.70271840379579</v>
+        <v>21.66693844372921</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.2671691644281069</v>
+        <v>0.6812827466472959</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.0085524781787345</v>
+        <v>0.0514943742334104</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>8071</v>
+        <v>8463</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>能率網通</t>
+          <t>潤泰材</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>319.9672316822559</v>
+        <v>320.9511533058237</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>21.75</v>
+        <v>21.2</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>42.75933846621131</v>
+        <v>49.5099278302382</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>9.960474984336718</v>
+        <v>26.70271905232586</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.6424088091267123</v>
+        <v>0.2671691644281069</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.0758575516202116</v>
+        <v>0.0085524784235318</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>8411</v>
+        <v>8071</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>福貞-KY</t>
+          <t>能率網通</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>317.6323125612178</v>
+        <v>319.9672316822559</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>11.75</v>
+        <v>21.75</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>28.76605499966402</v>
+        <v>42.75933847692557</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>36.71697128843091</v>
+        <v>9.960475002199448</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>2.031379645655545</v>
+        <v>0.6424088091267123</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.0562962731574766</v>
+        <v>0.07585755166471971</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>8114</v>
+        <v>8411</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>振樺電</t>
+          <t>福貞-KY</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>314.3803115676429</v>
+        <v>317.6323125612178</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>177.5</v>
+        <v>11.75</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>39.32970007741113</v>
+        <v>28.766054956971</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>24.50740266244284</v>
+        <v>36.71697137807788</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1.020412423518965</v>
+        <v>2.031379645655545</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>1.003513189976186</v>
+        <v>-0.0562962731463501</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>8097</v>
+        <v>8114</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>常珵</t>
+          <t>振樺電</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>312.3129270273699</v>
+        <v>314.3803115676429</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>48.2</v>
+        <v>177.5</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>38.68162058579145</v>
+        <v>39.32970007741113</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>17.61005384550385</v>
+        <v>24.50740289159818</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.4077260477119798</v>
+        <v>1.020412423518965</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.06483325241017431</v>
+        <v>1.003513191088885</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>8261</v>
+        <v>8097</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>富鼎</t>
+          <t>常珵</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>310.5989712904346</v>
+        <v>312.3129270273699</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>180.5</v>
+        <v>48.2</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>48.61898132755653</v>
+        <v>38.6816204483477</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>17.15197545495072</v>
+        <v>17.61005385355298</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>1.284509031381192</v>
+        <v>0.4077260477119798</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>2.359339893251683</v>
+        <v>0.0648332523656605</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>8087</v>
+        <v>8261</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>華鎂鑫</t>
+          <t>富鼎</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>304.6597532183895</v>
+        <v>310.5989712904346</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>22.85</v>
+        <v>180.5</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>48.18101952114881</v>
+        <v>48.61898133368651</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>5.134452550630399</v>
+        <v>17.15197553124404</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.4527522101787211</v>
+        <v>1.284509031381192</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.0670511741465961</v>
+        <v>2.359339893073635</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>9912</v>
+        <v>8087</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>偉聯</t>
+          <t>華鎂鑫</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>292.6278817436178</v>
+        <v>304.6597532183896</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>12.95</v>
+        <v>22.85</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>50.03724839991157</v>
+        <v>48.18101952296635</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>34.28269009944054</v>
+        <v>5.134452547981376</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.2737855717988168</v>
+        <v>0.4527522101787211</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.0067302870827471</v>
+        <v>0.0670511741577253</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>8422</v>
+        <v>9912</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>可寧衛*</t>
+          <t>偉聯</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>292.2536709837928</v>
+        <v>292.6278817436178</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>25.55</v>
+        <v>12.95</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,49 +4951,49 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>44.1138147586033</v>
+        <v>50.03724842008068</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>7.97500344114702</v>
+        <v>34.28269015400027</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.6654817331165166</v>
+        <v>0.2737855717988168</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L85" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M85" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.0136102700658637</v>
+        <v>-0.0067302870493656</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>8080</v>
+        <v>8422</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>永利聯合</t>
+          <t>可寧衛*</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>291.6562307362708</v>
+        <v>292.2536709837928</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>28.3</v>
+        <v>25.55</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,49 +5004,49 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>51.69482805583181</v>
+        <v>44.11381566872717</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>32.4633147360612</v>
+        <v>7.975003476572353</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.413418222611168</v>
+        <v>0.6654817331165166</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M86" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.1009603142668525</v>
+        <v>-0.0136102710193623</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>8176</v>
+        <v>8080</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>智捷</t>
+          <t>永利聯合</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>282.6055382257989</v>
+        <v>291.6562307362708</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>9.65</v>
+        <v>28.3</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>37.30767595457765</v>
+        <v>51.69482753190201</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>26.13846143754469</v>
+        <v>32.46331487373325</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.497673942166656</v>
+        <v>1.413418222611168</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.0072446636799695</v>
+        <v>0.1009603142557269</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>9930</v>
+        <v>8176</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>中聯資源</t>
+          <t>智捷</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>279.1479950597472</v>
+        <v>282.6055382257987</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>58.4</v>
+        <v>9.65</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>16.26069888891641</v>
+        <v>37.30767587746976</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>36.15212990796434</v>
+        <v>26.13846135011506</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.04537194403018</v>
+        <v>1.497673942166656</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,7 +5128,7 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.1743288727394808</v>
+        <v>-0.0072446634574273</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
@@ -5138,21 +5138,21 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>8940</v>
+        <v>9930</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>新天地</t>
+          <t>中聯資源</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>273.574056396484</v>
+        <v>279.1479950597467</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>15.15</v>
+        <v>58.4</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>53.51978103706713</v>
+        <v>16.26069884120197</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>11.42925390124908</v>
+        <v>36.15212986199487</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.2729448192959408</v>
+        <v>1.04537194403018</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.0484213543593818</v>
+        <v>-0.1743288727172258</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>8271</v>
+        <v>8940</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>新天地</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>273.1714851159185</v>
+        <v>273.5740563964841</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>199.5</v>
+        <v>15.15</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>39.24411812669221</v>
+        <v>53.51978085092245</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>12.94927336303709</v>
+        <v>11.42925392938144</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>1.020988026920266</v>
+        <v>0.2729448192959408</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.3233670560995421</v>
+        <v>0.0484213543037463</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>8404</v>
+        <v>8271</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>百和興業-KY</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>272.7764750283043</v>
+        <v>273.1714851159183</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>14</v>
+        <v>199.5</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>47.11690528039191</v>
+        <v>39.2441181299348</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>46.49694538809338</v>
+        <v>12.94927338308331</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.067541341736764</v>
+        <v>1.020988026920266</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.1096514110781363</v>
+        <v>0.3233670559437325</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>8478</v>
+        <v>8404</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>東哥遊艇</t>
+          <t>百和興業-KY</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>267.7887244624445</v>
+        <v>272.7764750283042</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>140</v>
+        <v>14</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>44.42287649227613</v>
+        <v>47.11690506183617</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>7.523932397838197</v>
+        <v>46.49694560027209</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1.199927762321393</v>
+        <v>1.067541341736764</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.131431049480365</v>
+        <v>0.1096514112116624</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
+          <t>market_above_ma60, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>8443</v>
+        <v>8478</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>阿瘦</t>
+          <t>東哥遊艇</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>265.1967268044963</v>
+        <v>267.7887244624446</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>11.15</v>
+        <v>140</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>44.61126946743668</v>
+        <v>44.4228761533243</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>52.49667381126385</v>
+        <v>7.523932378013983</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.9088271535977084</v>
+        <v>1.199927762321393</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.0037171415127127</v>
+        <v>0.1314310497029081</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>8049</v>
+        <v>8443</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>晶采</t>
+          <t>阿瘦</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>251.0241121846801</v>
+        <v>265.1967268044963</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>24.45</v>
+        <v>11.15</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>44.08451303498183</v>
+        <v>44.61126930798109</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>14.27682827353513</v>
+        <v>52.49667401250918</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.5238754844087758</v>
+        <v>0.9088271535977084</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.0373960929058961</v>
+        <v>0.003717141534968</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>8047</v>
+        <v>8049</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>星雲</t>
+          <t>晶采</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>247.3526021820113</v>
+        <v>251.0241121846801</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>44.5</v>
+        <v>24.45</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>50.27470371908093</v>
+        <v>44.08451299593214</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>8.957065055662214</v>
+        <v>14.27682828410773</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1.113023618742389</v>
+        <v>0.5238754844087758</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.7257028830165064</v>
+        <v>0.0373960928947667</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>8454</v>
+        <v>8047</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>星雲</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>241.2606117509233</v>
+        <v>247.3526021820107</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>241</v>
+        <v>44.5</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,49 +5534,49 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>47.2636585161961</v>
+        <v>50.27470372235318</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>11.72338530731126</v>
+        <v>8.957065075895995</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.4248457621423513</v>
+        <v>1.113023618742389</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L96" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M96" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.6324199216928257</v>
+        <v>0.7257028829608629</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>8088</v>
+        <v>8454</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>品安</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>241.1662747808778</v>
+        <v>241.2606117509233</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>43.8</v>
+        <v>241</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,49 +5587,49 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>49.76560309405741</v>
+        <v>47.26365857642308</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>13.65590901801227</v>
+        <v>11.72338521848564</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>1.256252621157641</v>
+        <v>0.4248457621423513</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L97" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M97" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.3767863554792056</v>
+        <v>0.6324199211364632</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>8163</v>
+        <v>8088</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>達方</t>
+          <t>品安</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>240.6094488777084</v>
+        <v>241.1662747808778</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>29.85</v>
+        <v>43.8</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>42.87981978215982</v>
+        <v>49.76560314618668</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>12.62838985523964</v>
+        <v>13.65590901646543</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.7551403039045136</v>
+        <v>1.256252621157641</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,7 +5658,7 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.0735396168775454</v>
+        <v>0.3767863554903351</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -5668,21 +5668,21 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>8101</v>
+        <v>8163</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>達方</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>229.8513971298647</v>
+        <v>240.6094488777084</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>10.3</v>
+        <v>29.85</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>42.34906424943771</v>
+        <v>42.87981992314916</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>16.44365345348984</v>
+        <v>12.6283898921754</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.1301251686168711</v>
+        <v>0.7551403039045136</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.1209711913522376</v>
+        <v>0.07353961685529251</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>8222</v>
+        <v>8101</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>寶一</t>
+          <t>華冠</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>222.8596613345446</v>
+        <v>229.8513971298646</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>35.1</v>
+        <v>10.3</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>40.73937908986601</v>
+        <v>42.34906414883429</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>8.794816761507381</v>
+        <v>16.44365345226704</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.3870128060262118</v>
+        <v>0.1301251686168711</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.1050530019045523</v>
+        <v>-0.1209711912520924</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>8341</v>
+        <v>8222</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>寶一</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>219.1407931165736</v>
+        <v>222.8596613345446</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>73.8</v>
+        <v>35.1</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>37.05648649339433</v>
+        <v>40.73938009094184</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>12.61022694218548</v>
+        <v>8.79481684222638</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.7273447076327048</v>
+        <v>0.3870128060262118</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.0298769800371778</v>
+        <v>0.1050530017710232</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>8429</v>
+        <v>8341</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>金麗-KY</t>
+          <t>日友</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>216.9587438241341</v>
+        <v>219.1407931165736</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>5.9</v>
+        <v>73.8</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>43.58420388337899</v>
+        <v>37.05648657506774</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>7.42116824247042</v>
+        <v>12.61022694312326</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.4531701565060215</v>
+        <v>0.7273447076327048</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,7 +5870,7 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.0056982307848195</v>
+        <v>-0.029876980103937</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
@@ -5880,21 +5880,21 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>8481</v>
+        <v>8429</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>政伸</t>
+          <t>金麗-KY</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>215.5256206284073</v>
+        <v>216.9587438241342</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>40.6</v>
+        <v>5.9</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>44.76596838628956</v>
+        <v>43.58420405043517</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>12.16080710908647</v>
+        <v>7.421168279513759</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.3809097872785837</v>
+        <v>0.4531701565060215</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,7 +5923,7 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.0491573665387746</v>
+        <v>0.005698230775918</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -5933,21 +5933,21 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>8367</v>
+        <v>8481</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>建新國際</t>
+          <t>政伸</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>214.9278119846296</v>
+        <v>215.5256206284074</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>40.9</v>
+        <v>40.6</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>53.92689326593881</v>
+        <v>44.76596797719962</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>14.43765880680657</v>
+        <v>12.1608071468484</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>1.045493223751115</v>
+        <v>0.3809097872785837</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.0423349824143802</v>
+        <v>-0.0491573663829944</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>8249</v>
+        <v>8367</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>菱光</t>
+          <t>建新國際</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>207.2533452155258</v>
+        <v>214.9278119846296</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>39.3</v>
+        <v>40.9</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>46.43233019982648</v>
+        <v>53.92689334659694</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>15.45636347983578</v>
+        <v>14.43765889412709</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.3948254321441044</v>
+        <v>1.045493223751115</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.1830199944782504</v>
+        <v>0.0423349823476202</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>8472</v>
+        <v>8249</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>夠麻吉</t>
+          <t>菱光</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>206.9159547138248</v>
+        <v>207.2533452155243</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>67.90000000000001</v>
+        <v>39.3</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>40.30402113874221</v>
+        <v>46.43233050633585</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>27.99119885115016</v>
+        <v>15.45636345813229</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.0915954713824829</v>
+        <v>0.3948254321441044</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-1.158458078091411</v>
+        <v>0.1830199942334583</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>8374</v>
+        <v>8472</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>羅昇</t>
+          <t>夠麻吉</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>183.6479593256477</v>
+        <v>206.9159547138248</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>74.09999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>36.58205599504508</v>
+        <v>40.30402073533084</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>10.15759220215351</v>
+        <v>27.99119920105399</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>1.391547480317337</v>
+        <v>0.0915954713824829</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.06703110281023431</v>
+        <v>-1.15845807655587</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>9136</v>
+        <v>8374</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>巨騰-DR</t>
+          <t>羅昇</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>177.8010407732407</v>
+        <v>183.6479593256479</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>9.199999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>32.33699036969996</v>
+        <v>36.58205565005205</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>17.03304013099863</v>
+        <v>10.15759231702086</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.7136039970620186</v>
+        <v>1.391547480317337</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.0623463217536578</v>
+        <v>-0.0670311014749827</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>8044</v>
+        <v>9136</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>網家</t>
+          <t>巨騰-DR</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>177.1272120300522</v>
+        <v>177.8010407732407</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>24.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>50.00508977179712</v>
+        <v>32.33699037530904</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>17.16102168493185</v>
+        <v>17.03304013043113</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.5176419555989005</v>
+        <v>0.7136039970620186</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.1096968623428562</v>
+        <v>0.0623463217892638</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>8390</v>
+        <v>8044</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>金益鼎</t>
+          <t>網家</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>146.0612632875093</v>
+        <v>177.1272120300521</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>90.90000000000001</v>
+        <v>24.2</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>43.10246644054228</v>
+        <v>50.00508989235949</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>19.73462802218262</v>
+        <v>17.16102169162326</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.9333942982762388</v>
+        <v>0.5176419555989005</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.2998225699233439</v>
+        <v>0.1096968622204609</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6304,21 +6304,21 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>8487</v>
+        <v>8390</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>愛爾達-創</t>
+          <t>金益鼎</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>145.8629940830281</v>
+        <v>146.0612632875095</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>70.09999999999999</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,16 +6329,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>42.90424347012134</v>
+        <v>43.10246644545018</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>11.69162779358256</v>
+        <v>19.73462802626165</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.4024438372040744</v>
+        <v>0.9333942982762388</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.0160860633833634</v>
+        <v>0.2998225699010921</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6357,21 +6357,21 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>8067</v>
+        <v>8487</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>志旭</t>
+          <t>愛爾達-創</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>144.8572864131396</v>
+        <v>145.8629940830281</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>11.5</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>44.57729336615932</v>
+        <v>42.90424339535345</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>17.10783958010294</v>
+        <v>11.69162783546806</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.0983745110757316</v>
+        <v>0.4024438372040744</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,62 +6400,115 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.0373666358761561</v>
+        <v>0.0160860633166056</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
+        <v>8067</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>志旭</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>144.8572864131397</v>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>44.57729103507442</v>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>17.10783972056232</v>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>0.0983745110757316</v>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N113" s="2" t="n">
+        <v>-0.0373666358650294</v>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
         <v>8291</v>
       </c>
-      <c r="B113" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>尚茂</t>
         </is>
       </c>
-      <c r="C113" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D113" s="2" t="n">
+      <c r="C114" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D114" s="2" t="n">
         <v>101.7225705293791</v>
       </c>
-      <c r="E113" s="2" t="n">
+      <c r="E114" s="2" t="n">
         <v>27.3</v>
       </c>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="G113" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H113" s="2" t="n">
-        <v>36.37913982056623</v>
-      </c>
-      <c r="I113" s="2" t="n">
-        <v>5.328390798220692</v>
-      </c>
-      <c r="J113" s="2" t="n">
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>36.37939091386696</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>5.328014816327801</v>
+      </c>
+      <c r="J114" s="2" t="n">
         <v>0.4352871123868269</v>
       </c>
-      <c r="K113" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L113" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M113" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N113" s="2" t="n">
-        <v>0.0430478715553799</v>
-      </c>
-      <c r="O113" s="2" t="inlineStr">
+      <c r="K114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N114" s="2" t="n">
+        <v>0.0430417503419926</v>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>

--- a/output/full_scan/batch_seq0_2026-10-08.xlsx
+++ b/output/full_scan/batch_seq0_2026-10-08.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O114"/>
+  <dimension ref="A1:O116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1693,21 +1693,21 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>8091</v>
+        <v>8358</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>翔名</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>655.4345781659791</v>
+        <v>657.2938661976115</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>230</v>
+        <v>535</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>57.41382261893338</v>
+        <v>56.59023388916533</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>21.01761265133142</v>
+        <v>28.71494105480638</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.6416039055495474</v>
+        <v>0.2350209485263015</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>2.612266514993742</v>
+        <v>2.490123632503291</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>8131</v>
+        <v>8091</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>福懋科</t>
+          <t>翔名</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>653.8829524402263</v>
+        <v>655.4345781659791</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>68</v>
+        <v>230</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>68.28773730178901</v>
+        <v>57.41382261893338</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>15.8947929021889</v>
+        <v>21.01761265133142</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>2.922459904062402</v>
+        <v>0.6416039055495474</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.863253676281051</v>
+        <v>2.612266514993742</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8240</v>
+        <v>8131</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>華宏</t>
+          <t>福懋科</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>626.8801999860286</v>
+        <v>653.8829524402263</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>54.5</v>
+        <v>68</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>55.20473590781823</v>
+        <v>68.28773730178901</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>37.57523380679167</v>
+        <v>15.8947929021889</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.2622878238583767</v>
+        <v>2.922459904062402</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.0543360403054329</v>
+        <v>0.863253676281051</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>8299</v>
+        <v>8240</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>華宏</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>619.9120315310141</v>
+        <v>626.8801999860286</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>2060</v>
+        <v>54.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,49 +1877,49 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>47.78381090987602</v>
+        <v>55.20473590781823</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>12.5987322285307</v>
+        <v>37.57523380679167</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.6813679857092976</v>
+        <v>0.2622878238583767</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-6.808955191873824</v>
+        <v>-0.0543360403054329</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>8112</v>
+        <v>8299</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>612.5266647546071</v>
+        <v>619.9120315310141</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>85.09999999999999</v>
+        <v>2060</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,49 +1930,49 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>49.11929440422172</v>
+        <v>47.78381090987602</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>19.00406645416426</v>
+        <v>12.5987322285307</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>2.064014355832512</v>
+        <v>0.6813679857092976</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M28" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.3928557141328472</v>
+        <v>-6.808955191873824</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>8215</v>
+        <v>8112</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>明基材</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>595.0502141518805</v>
+        <v>612.5266647546071</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>28</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>54.47009015855016</v>
+        <v>49.11929440422172</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>38.52500912334865</v>
+        <v>19.00406645416426</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.2039126708344463</v>
+        <v>2.064014355832512</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.0536524989102179</v>
+        <v>0.3928557141328472</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>8482</v>
+        <v>8215</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>商億-KY</t>
+          <t>明基材</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>592.9609450057658</v>
+        <v>595.0502141518805</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>50.1</v>
+        <v>28</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>55.83982313956914</v>
+        <v>54.47009015855016</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>4.15883751812657</v>
+        <v>38.52500912334865</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.3131403187712136</v>
+        <v>0.2039126708344463</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.1419729024590614</v>
+        <v>-0.0536524989102179</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>8064</v>
+        <v>8482</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>東捷</t>
+          <t>商億-KY</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>587.8994877323606</v>
+        <v>592.9609450057658</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>133.5</v>
+        <v>50.1</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>55.07556762034065</v>
+        <v>55.83982313956914</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>23.30970629242927</v>
+        <v>4.15883751812657</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.1556558365170188</v>
+        <v>0.3131403187712136</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.8245204238784813</v>
+        <v>0.1419729024590614</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>8089</v>
+        <v>8064</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>康全電訊</t>
+          <t>東捷</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>580.6920907104044</v>
+        <v>587.8994877323606</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>19.4</v>
+        <v>133.5</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>58.98850584969143</v>
+        <v>55.07556762034065</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>28.8338775140695</v>
+        <v>23.30970629242927</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.5116185890333</v>
+        <v>0.1556558365170188</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.0367323419004866</v>
+        <v>-0.8245204238784813</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>8074</v>
+        <v>8089</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>鉅橡</t>
+          <t>康全電訊</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>573.2361473756329</v>
+        <v>580.6920907104044</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>56.5</v>
+        <v>19.4</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>58.74807538178406</v>
+        <v>58.98850584969143</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>22.86551436745738</v>
+        <v>28.8338775140695</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.108350446873547</v>
+        <v>0.5116185890333</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.9196934811197246</v>
+        <v>0.0367323419004866</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>8155</v>
+        <v>8074</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>博智</t>
+          <t>鉅橡</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>561.6707711957353</v>
+        <v>573.2361473756329</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>326.5</v>
+        <v>56.5</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>48.75616725156184</v>
+        <v>58.74807538178406</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>12.04954635460285</v>
+        <v>22.86551436745738</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.6845297377637236</v>
+        <v>1.108350446873547</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.2254880767101654</v>
+        <v>0.9196934811197246</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>9105</v>
+        <v>8155</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>博智</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>555.3485885976603</v>
+        <v>561.6707711957353</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>8.630000000000001</v>
+        <v>326.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>53.37589158422116</v>
+        <v>48.75616725156184</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>19.95622744640882</v>
+        <v>12.04954635460285</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.06436812333298</v>
+        <v>0.6845297377637236</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,7 +2319,7 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.0257830548826195</v>
+        <v>0.2254880767101654</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2329,21 +2329,21 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>8109</v>
+        <v>9105</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>博大</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>545.237332850558</v>
+        <v>555.3485885976603</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>136</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>53.29672523006876</v>
+        <v>53.37589158422116</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>27.9068990583525</v>
+        <v>19.95622744640882</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.5209096159834906</v>
+        <v>1.06436812333298</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.2432142382569972</v>
+        <v>0.0257830548826195</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>8464</v>
+        <v>8109</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>博大</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>534.6256349263429</v>
+        <v>545.237332850558</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>366.5</v>
+        <v>136</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,49 +2407,49 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>47.11262062905258</v>
+        <v>53.29672523006876</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>10.34898960042178</v>
+        <v>27.9068990583525</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.6407564156104073</v>
+        <v>0.5209096159834906</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.717665441127562</v>
+        <v>0.2432142382569972</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, invest_trust_buy_2d, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>8040</v>
+        <v>8464</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>九暘</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>529.7791231467975</v>
+        <v>534.6256349263429</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>89</v>
+        <v>366.5</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,49 +2460,49 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>54.59729309788906</v>
+        <v>47.11262062905258</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>28.0369515793599</v>
+        <v>10.34898960042178</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.3314914356505022</v>
+        <v>0.6407564156104073</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M38" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-0.1768901601868906</v>
+        <v>-0.717665441127562</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, invest_trust_buy_2d, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>8110</v>
+        <v>8040</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>華東</t>
+          <t>九暘</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>526.6371552296055</v>
+        <v>529.7791231467975</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>49.25</v>
+        <v>89</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>57.70629572668711</v>
+        <v>54.59729309788906</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>28.15750577498932</v>
+        <v>28.0369515793599</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.4782481924665126</v>
+        <v>0.3314914356505022</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.1912227348127948</v>
+        <v>-0.1768901601868906</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>8438</v>
+        <v>8110</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>昶昕</t>
+          <t>華東</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>525.6820237232134</v>
+        <v>526.6371552296055</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>80.90000000000001</v>
+        <v>49.25</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>64.76987253322193</v>
+        <v>57.70629572668711</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>32.53685413188181</v>
+        <v>28.15750577498932</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.5670663761275974</v>
+        <v>0.4782481924665126</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.7175200451707395</v>
+        <v>0.1912227348127948</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>8227</v>
+        <v>8438</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>巨有科技</t>
+          <t>昶昕</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>523.0926847156088</v>
+        <v>525.6820237232134</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>335</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>65.40637199469262</v>
+        <v>64.76987253322193</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>49.07272363073445</v>
+        <v>32.53685413188181</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.3507565649380665</v>
+        <v>0.5670663761275974</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>1.505232419359622</v>
+        <v>0.7175200451707395</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>8050</v>
+        <v>8227</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>廣積</t>
+          <t>巨有科技</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>521.7783768168604</v>
+        <v>523.0926847156088</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>60.4</v>
+        <v>335</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>52.38533300237361</v>
+        <v>65.40637199469262</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>27.28451893778002</v>
+        <v>49.07272363073445</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.5146268722717706</v>
+        <v>0.3507565649380665</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.0012711431299166</v>
+        <v>1.505232419359622</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>9955</v>
+        <v>8050</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>佳龍</t>
+          <t>廣積</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>515.1378922641563</v>
+        <v>521.7783768168604</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>24.1</v>
+        <v>60.4</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>56.830794914371</v>
+        <v>52.38533300237361</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>13.91453306425982</v>
+        <v>27.28451893778002</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>2.392350724340234</v>
+        <v>0.5146268722717706</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.1424846873738943</v>
+        <v>0.0012711431299166</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>8093</v>
+        <v>9955</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>保銳</t>
+          <t>佳龍</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>510.8726056327984</v>
+        <v>515.1378922641563</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>26.3</v>
+        <v>24.1</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>54.20933332074446</v>
+        <v>56.830794914371</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>12.78522607080232</v>
+        <v>13.91453306425982</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.171671703038444</v>
+        <v>2.392350724340234</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>1</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.220507016725546</v>
+        <v>0.1424846873738943</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>8103</v>
+        <v>8093</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>瀚荃</t>
+          <t>保銳</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>470.3182288805356</v>
+        <v>510.8726056327984</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>114.5</v>
+        <v>26.3</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>47.65076332000302</v>
+        <v>54.20933332074446</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>34.00702985134878</v>
+        <v>12.78522607080232</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.3792983774624572</v>
+        <v>1.171671703038444</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-1.895591269792043</v>
+        <v>0.220507016725546</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>8431</v>
+        <v>8103</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>匯鑽科</t>
+          <t>瀚荃</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>466.6384434013606</v>
+        <v>470.3182288805356</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>59.6</v>
+        <v>114.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>47.42181609444074</v>
+        <v>47.65076332000302</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>30.8976432166122</v>
+        <v>34.00702985134878</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.8821235310731542</v>
+        <v>0.3792983774624572</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.8736886222309268</v>
+        <v>-1.895591269792043</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>8054</v>
+        <v>8431</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>安國</t>
+          <t>匯鑽科</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>461.0112710596544</v>
+        <v>466.6384434013606</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>81</v>
+        <v>59.6</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>40.58445084506695</v>
+        <v>47.42181609444074</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>22.48321764170405</v>
+        <v>30.8976432166122</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.5953315198623444</v>
+        <v>0.8821235310731542</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.3258135906609768</v>
+        <v>-0.8736886222309268</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>8234</v>
+        <v>8054</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>新漢</t>
+          <t>安國</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>460.538957417092</v>
+        <v>461.0112710596544</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>63.4</v>
+        <v>81</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>49.26418390999588</v>
+        <v>40.58445084506695</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>17.75820008719286</v>
+        <v>22.48321764170405</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.565331861728069</v>
+        <v>0.5953315198623444</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.2312142095599967</v>
+        <v>-0.3258135906609768</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>8467</v>
+        <v>8234</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>波力-KY</t>
+          <t>新漢</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>458.3304688996722</v>
+        <v>460.538957417092</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>90.7</v>
+        <v>63.4</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>51.24182341014726</v>
+        <v>49.26418390999588</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>7.409446058844591</v>
+        <v>17.75820008719286</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.4348522983750438</v>
+        <v>1.565331861728069</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.8011644501649202</v>
+        <v>0.2312142095599967</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>8932</v>
+        <v>8467</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>智通*</t>
+          <t>波力-KY</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>456.8992214466853</v>
+        <v>458.3304688996722</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>92.7</v>
+        <v>90.7</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>47.85265698818198</v>
+        <v>51.24182341014726</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>16.90142867001112</v>
+        <v>7.409446058844591</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.207241727081338</v>
+        <v>0.4348522983750438</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.4152180221018553</v>
+        <v>0.8011644501649202</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>8102</v>
+        <v>8932</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>傑霖科技</t>
+          <t>智通*</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>455.7379059819353</v>
+        <v>456.8992214466853</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>60.5</v>
+        <v>92.7</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>51.09471769887392</v>
+        <v>47.85265698818198</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>5.215468956324937</v>
+        <v>16.90142867001112</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.061167350748045</v>
+        <v>1.207241727081338</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>1.315487352717326</v>
+        <v>0.4152180221018553</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>8410</v>
+        <v>8102</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>森田</t>
+          <t>傑霖科技</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>453.378734983228</v>
+        <v>455.7379059819353</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>26.45</v>
+        <v>60.5</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>19.97018239934931</v>
+        <v>51.09471769887392</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>49.04285851443795</v>
+        <v>5.215468956324937</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1.606984700735965</v>
+        <v>1.061167350748045</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.1275823386673414</v>
+        <v>1.315487352717326</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>8121</v>
+        <v>8410</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>越峰</t>
+          <t>森田</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>447.0431000301944</v>
+        <v>453.378734983228</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>34.4</v>
+        <v>26.45</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>65.5662966628927</v>
+        <v>19.97018239934931</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>33.14428458119747</v>
+        <v>49.04285851443795</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>2.228843037556953</v>
+        <v>1.606984700735965</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.6710381744245847</v>
+        <v>-0.1275823386673414</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>8070</v>
+        <v>8121</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>越峰</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>439.2716921379535</v>
+        <v>447.0431000301944</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>50.5</v>
+        <v>34.4</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,49 +3308,49 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>51.64396867004989</v>
+        <v>65.5662966628927</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>17.95076643234812</v>
+        <v>33.14428458119747</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.261462616369482</v>
+        <v>2.228843037556953</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.1092348924513225</v>
+        <v>0.6710381744245847</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>8383</v>
+        <v>8070</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>千附</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>432.7185481448347</v>
+        <v>439.2716921379535</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>69</v>
+        <v>50.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,25 +3361,25 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>53.70635728600141</v>
+        <v>51.64396867004989</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>18.66799548297174</v>
+        <v>17.95076643234812</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.7225547931200471</v>
+        <v>1.261462616369482</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.4690026349035413</v>
+        <v>0.1092348924513225</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -3389,21 +3389,21 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>8059</v>
+        <v>8383</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>凱碩</t>
+          <t>千附</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>424.7820793364625</v>
+        <v>432.7185481448347</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>17.6</v>
+        <v>69</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>60.25695172624757</v>
+        <v>53.70635728600141</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>27.2311602706</v>
+        <v>18.66799548297174</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.24034330025339</v>
+        <v>0.7225547931200471</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.1234104521283996</v>
+        <v>0.4690026349035413</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>8072</v>
+        <v>8059</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>陞泰</t>
+          <t>凱碩</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>420.468522814218</v>
+        <v>424.7820793364625</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>26.9</v>
+        <v>17.6</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>48.05622873834169</v>
+        <v>60.25695172624757</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>36.87661600599267</v>
+        <v>27.2311602706</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.4191745087014877</v>
+        <v>0.24034330025339</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.0617997258459984</v>
+        <v>0.1234104521283996</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>8147</v>
+        <v>8072</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>正淩</t>
+          <t>陞泰</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>414.2031695476912</v>
+        <v>420.468522814218</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>139</v>
+        <v>26.9</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>52.08418875083346</v>
+        <v>48.05622873834169</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>31.04128221608954</v>
+        <v>36.87661600599267</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.432183151738959</v>
+        <v>0.4191745087014877</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.2512553510402679</v>
+        <v>-0.0617997258459984</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>8104</v>
+        <v>8147</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>錸寶</t>
+          <t>正淩</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>410.3640017409354</v>
+        <v>414.2031695476912</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>30.95</v>
+        <v>139</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>48.57514128544108</v>
+        <v>52.08418875083346</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>16.00618360180705</v>
+        <v>31.04128221608954</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.6734366827199414</v>
+        <v>0.432183151738959</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.082402606448088</v>
+        <v>-0.2512553510402679</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>8096</v>
+        <v>8104</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>錸寶</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>404.2055890913488</v>
+        <v>410.3640017409354</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>90.3</v>
+        <v>30.95</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>41.87255004124982</v>
+        <v>48.57514128544108</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>31.70957464210655</v>
+        <v>16.00618360180705</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.5161376373223423</v>
+        <v>0.6734366827199414</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>1.538462846434086</v>
+        <v>0.082402606448088</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>8092</v>
+        <v>8096</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>建暐</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>403.2234296852506</v>
+        <v>404.2055890913488</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>12.75</v>
+        <v>90.3</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>51.66410364899698</v>
+        <v>41.87255004124982</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>13.64569296770591</v>
+        <v>31.70957464210655</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>3.650182642688881</v>
+        <v>0.5161376373223423</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.016754974943874</v>
+        <v>1.538462846434086</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>8277</v>
+        <v>8092</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>商丞</t>
+          <t>建暐</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>401.2868373581581</v>
+        <v>403.2234296852506</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>15.45</v>
+        <v>12.75</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>78.68008853777276</v>
+        <v>51.66410364899698</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>37.30805682429794</v>
+        <v>13.64569296770591</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.1808425508974529</v>
+        <v>3.650182642688881</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.1343239081888085</v>
+        <v>-0.016754974943874</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>8423</v>
+        <v>8277</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>保綠-KY</t>
+          <t>商丞</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>398.9345315449172</v>
+        <v>401.2868373581581</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>17.8</v>
+        <v>15.45</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>44.94763305541719</v>
+        <v>78.68008853777276</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>20.60234961324448</v>
+        <v>37.30805682429794</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.6610502872841946</v>
+        <v>0.1808425508974529</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.0228012556361702</v>
+        <v>0.1343239081888085</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>8473</v>
+        <v>8423</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>山林水</t>
+          <t>保綠-KY</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>396.8480202651788</v>
+        <v>398.9345315449172</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>39.8</v>
+        <v>17.8</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>44.64499201724888</v>
+        <v>44.94763305541719</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>21.39136576494574</v>
+        <v>20.60234961324448</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.5692080331342624</v>
+        <v>0.6610502872841946</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,7 +3856,7 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.3123991656391873</v>
+        <v>-0.0228012556361702</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -3866,41 +3866,41 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>8183</v>
+        <v>8473</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>精星</t>
+          <t>山林水</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>395.8634049635209</v>
+        <v>396.8480202651788</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>28.2</v>
+        <v>39.8</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G65" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>44.90268834399803</v>
+        <v>44.64499201724888</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>19.1453761405531</v>
+        <v>21.39136576494574</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.870816255095116</v>
+        <v>0.5692080331342624</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,48 +3909,48 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.068620610797997</v>
+        <v>0.3123991656391873</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>8210</v>
+        <v>8183</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>精星</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>389.1256232099181</v>
+        <v>395.8634049635209</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>874</v>
+        <v>28.2</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G66" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>42.30937054187002</v>
+        <v>44.90268834399803</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>18.9829820197608</v>
+        <v>19.1453761405531</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.9402414291795336</v>
+        <v>1.870816255095116</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>5.455581065764903</v>
+        <v>0.068620610797997</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>8499</v>
+        <v>8210</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>鼎炫-KY</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>385.4744141746589</v>
+        <v>389.1256232099181</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>253.5</v>
+        <v>874</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>50.85390714794104</v>
+        <v>42.30937054187002</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>8.51251650267225</v>
+        <v>18.9829820197608</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.3401844706912896</v>
+        <v>0.9402414291795336</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>2.469308960224295</v>
+        <v>5.455581065764903</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>8440</v>
+        <v>8084</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>綠電</t>
+          <t>巨虹</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>381.883635821929</v>
+        <v>385.5783498514359</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>20.1</v>
+        <v>14.4</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>48.47937300937726</v>
+        <v>6.875745473777286</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>18.189632038254</v>
+        <v>51.46279706647394</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.5895896159336576</v>
+        <v>0.5092614232296112</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.0076392896313175</v>
+        <v>-2.141603142138662</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>8462</v>
+        <v>8499</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>柏文</t>
+          <t>鼎炫-KY</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>373.6262227857153</v>
+        <v>385.4744141746589</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>156</v>
+        <v>253.5</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>37.31450991342541</v>
+        <v>50.85390714794104</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>32.27104997860098</v>
+        <v>8.51251650267225</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>2.027341329392833</v>
+        <v>0.3401844706912896</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.06564547922579141</v>
+        <v>2.469308960224295</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>8069</v>
+        <v>8440</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>元太</t>
+          <t>綠電</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>368.4434208113037</v>
+        <v>381.883635821929</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>144</v>
+        <v>20.1</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,49 +4156,49 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>40.36133842359701</v>
+        <v>48.47937300937726</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>27.1671622292828</v>
+        <v>18.189632038254</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.5989563875292683</v>
+        <v>0.5895896159336576</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L70" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>1.113482669414593</v>
+        <v>-0.0076392896313175</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>8477</v>
+        <v>8462</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>創業家</t>
+          <t>柏文</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>363.8756244375477</v>
+        <v>373.6262227857153</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>13.5</v>
+        <v>156</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>28.91138071499005</v>
+        <v>37.31450991342541</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>27.43463926876743</v>
+        <v>32.27104997860098</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>3.017999211374759</v>
+        <v>2.027341329392833</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,7 +4227,7 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.07199120157396439</v>
+        <v>-0.06564547922579141</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
@@ -4237,21 +4237,21 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>8488</v>
+        <v>8069</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>吉源-KY</t>
+          <t>元太</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>347.4869459581391</v>
+        <v>368.4434208113037</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,49 +4262,49 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>8.186849530617351</v>
+        <v>40.36133842359701</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>38.91875935043327</v>
+        <v>27.1671622292828</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0</v>
+        <v>0.5989563875292683</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M72" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.6442186113205489</v>
+        <v>1.113482669414593</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>8455</v>
+        <v>8477</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>大拓-KY</t>
+          <t>創業家</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>342.2541318927333</v>
+        <v>363.8756244375477</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>37.93765132727655</v>
+        <v>28.91138071499005</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>10.29191459269391</v>
+        <v>27.43463926876743</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.1481788815458021</v>
+        <v>3.017999211374759</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-1.025581048485533</v>
+        <v>-0.07199120157396439</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>8105</v>
+        <v>8488</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>凌巨</t>
+          <t>吉源-KY</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>341.3092678897987</v>
+        <v>347.4869459581391</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>46.36827816468684</v>
+        <v>8.186849530617351</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>19.82358684480572</v>
+        <v>38.91875935043327</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.6231276079596844</v>
+        <v>0</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.08094866985133729</v>
+        <v>-0.6442186113205489</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>8466</v>
+        <v>8455</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>美吉吉-KY</t>
+          <t>大拓-KY</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>339.6344894061998</v>
+        <v>342.2541318927333</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>15.05</v>
+        <v>0</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>47.36883121178813</v>
+        <v>37.93765132727655</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>25.76774569806857</v>
+        <v>10.29191459269391</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.4300255712662324</v>
+        <v>0.1481788815458021</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.0704358580365383</v>
+        <v>-1.025581048485533</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>8048</v>
+        <v>8105</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>德勝</t>
+          <t>凌巨</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>328.0107544953105</v>
+        <v>341.3092678897987</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>51.4</v>
+        <v>15</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>54.4546393564756</v>
+        <v>46.36827816468684</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>12.93439385840971</v>
+        <v>19.82358684480572</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.8082742977947626</v>
+        <v>0.6231276079596844</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.3510327509488143</v>
+        <v>0.08094866985133729</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>8076</v>
+        <v>8466</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>伍豐</t>
+          <t>美吉吉-KY</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>325.5823637249029</v>
+        <v>339.6344894061998</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>21.4</v>
+        <v>15.05</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>40.96968395903292</v>
+        <v>47.36883121178813</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>21.66693844372921</v>
+        <v>25.76774569806857</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.6812827466472959</v>
+        <v>0.4300255712662324</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.0514943742334104</v>
+        <v>0.0704358580365383</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>8463</v>
+        <v>8048</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>潤泰材</t>
+          <t>德勝</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>320.9511533058237</v>
+        <v>328.0107544953105</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>21.2</v>
+        <v>51.4</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>49.5099278302382</v>
+        <v>54.4546393564756</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>26.70271905232586</v>
+        <v>12.93439385840971</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.2671691644281069</v>
+        <v>0.8082742977947626</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.0085524784235318</v>
+        <v>0.3510327509488143</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>8071</v>
+        <v>8076</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>能率網通</t>
+          <t>伍豐</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>319.9672316822559</v>
+        <v>325.5823637249029</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>21.75</v>
+        <v>21.4</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>42.75933847692557</v>
+        <v>40.96968395903292</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>9.960475002199448</v>
+        <v>21.66693844372921</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.6424088091267123</v>
+        <v>0.6812827466472959</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.07585755166471971</v>
+        <v>0.0514943742334104</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>8411</v>
+        <v>8463</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>福貞-KY</t>
+          <t>潤泰材</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>317.6323125612178</v>
+        <v>320.9511533058237</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>11.75</v>
+        <v>21.2</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>28.766054956971</v>
+        <v>49.5099278302382</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>36.71697137807788</v>
+        <v>26.70271905232586</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>2.031379645655545</v>
+        <v>0.2671691644281069</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.0562962731463501</v>
+        <v>0.0085524784235318</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>8114</v>
+        <v>8071</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>振樺電</t>
+          <t>能率網通</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>314.3803115676429</v>
+        <v>319.9672316822559</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>177.5</v>
+        <v>21.75</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>39.32970007741113</v>
+        <v>42.75933847692557</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>24.50740289159818</v>
+        <v>9.960475002199448</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.020412423518965</v>
+        <v>0.6424088091267123</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>1.003513191088885</v>
+        <v>0.07585755166471971</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>8097</v>
+        <v>8411</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>常珵</t>
+          <t>福貞-KY</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>312.3129270273699</v>
+        <v>317.6323125612178</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>48.2</v>
+        <v>11.75</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>38.6816204483477</v>
+        <v>28.766054956971</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>17.61005385355298</v>
+        <v>36.71697137807788</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.4077260477119798</v>
+        <v>2.031379645655545</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.0648332523656605</v>
+        <v>-0.0562962731463501</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>8261</v>
+        <v>8114</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>富鼎</t>
+          <t>振樺電</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>310.5989712904346</v>
+        <v>314.3803115676429</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>180.5</v>
+        <v>177.5</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>48.61898133368651</v>
+        <v>39.32970007741113</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>17.15197553124404</v>
+        <v>24.50740289159818</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>1.284509031381192</v>
+        <v>1.020412423518965</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>2.359339893073635</v>
+        <v>1.003513191088885</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>8087</v>
+        <v>8097</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>華鎂鑫</t>
+          <t>常珵</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>304.6597532183896</v>
+        <v>312.3129270273699</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>22.85</v>
+        <v>48.2</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>48.18101952296635</v>
+        <v>38.6816204483477</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>5.134452547981376</v>
+        <v>17.61005385355298</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.4527522101787211</v>
+        <v>0.4077260477119798</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.0670511741577253</v>
+        <v>0.0648332523656605</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>9912</v>
+        <v>8261</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>偉聯</t>
+          <t>富鼎</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>292.6278817436178</v>
+        <v>310.5989712904346</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>12.95</v>
+        <v>180.5</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>50.03724842008068</v>
+        <v>48.61898133368651</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>34.28269015400027</v>
+        <v>17.15197553124404</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.2737855717988168</v>
+        <v>1.284509031381192</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.0067302870493656</v>
+        <v>2.359339893073635</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>8422</v>
+        <v>8087</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>可寧衛*</t>
+          <t>華鎂鑫</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>292.2536709837928</v>
+        <v>304.6597532183896</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>25.55</v>
+        <v>22.85</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,49 +5004,49 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>44.11381566872717</v>
+        <v>48.18101952296635</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>7.975003476572353</v>
+        <v>5.134452547981376</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.6654817331165166</v>
+        <v>0.4527522101787211</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L86" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M86" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.0136102710193623</v>
+        <v>0.0670511741577253</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>8080</v>
+        <v>9912</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>永利聯合</t>
+          <t>偉聯</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>291.6562307362708</v>
+        <v>292.6278817436178</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>28.3</v>
+        <v>12.95</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>51.69482753190201</v>
+        <v>50.03724842008068</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>32.46331487373325</v>
+        <v>34.28269015400027</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.413418222611168</v>
+        <v>0.2737855717988168</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.1009603142557269</v>
+        <v>-0.0067302870493656</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>8176</v>
+        <v>8422</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>智捷</t>
+          <t>可寧衛*</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>282.6055382257987</v>
+        <v>292.2536709837928</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>9.65</v>
+        <v>25.55</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,49 +5110,49 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>37.30767587746976</v>
+        <v>44.11381566872717</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>26.13846135011506</v>
+        <v>7.975003476572353</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.497673942166656</v>
+        <v>0.6654817331165166</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.0072446634574273</v>
+        <v>-0.0136102710193623</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>9930</v>
+        <v>8080</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>中聯資源</t>
+          <t>永利聯合</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>279.1479950597467</v>
+        <v>291.6562307362708</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>58.4</v>
+        <v>28.3</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>16.26069884120197</v>
+        <v>51.69482753190201</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>36.15212986199487</v>
+        <v>32.46331487373325</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.04537194403018</v>
+        <v>1.413418222611168</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.1743288727172258</v>
+        <v>0.1009603142557269</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>8940</v>
+        <v>8176</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>新天地</t>
+          <t>智捷</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>273.5740563964841</v>
+        <v>282.6055382257987</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>15.15</v>
+        <v>9.65</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>53.51978085092245</v>
+        <v>37.30767587746976</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>11.42925392938144</v>
+        <v>26.13846135011506</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.2729448192959408</v>
+        <v>1.497673942166656</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.0484213543037463</v>
+        <v>-0.0072446634574273</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>8271</v>
+        <v>9930</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>中聯資源</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>273.1714851159183</v>
+        <v>279.1479950597467</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>199.5</v>
+        <v>58.4</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>39.2441181299348</v>
+        <v>16.26069884120197</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>12.94927338308331</v>
+        <v>36.15212986199487</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.020988026920266</v>
+        <v>1.04537194403018</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.3233670559437325</v>
+        <v>-0.1743288727172258</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>8404</v>
+        <v>8940</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>百和興業-KY</t>
+          <t>新天地</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>272.7764750283042</v>
+        <v>273.5740563964841</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>14</v>
+        <v>15.15</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>47.11690506183617</v>
+        <v>53.51978085092245</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>46.49694560027209</v>
+        <v>11.42925392938144</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1.067541341736764</v>
+        <v>0.2729448192959408</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.1096514112116624</v>
+        <v>0.0484213543037463</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, stronger_than_market</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>8478</v>
+        <v>8271</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>東哥遊艇</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>267.7887244624446</v>
+        <v>273.1714851159183</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>140</v>
+        <v>199.5</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>44.4228761533243</v>
+        <v>39.2441181299348</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>7.523932378013983</v>
+        <v>12.94927338308331</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>1.199927762321393</v>
+        <v>1.020988026920266</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.1314310497029081</v>
+        <v>0.3233670559437325</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>8443</v>
+        <v>8404</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>阿瘦</t>
+          <t>百和興業-KY</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>265.1967268044963</v>
+        <v>272.7764750283042</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>11.15</v>
+        <v>14</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>44.61126930798109</v>
+        <v>47.11690506183617</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>52.49667401250918</v>
+        <v>46.49694560027209</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.9088271535977084</v>
+        <v>1.067541341736764</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.003717141534968</v>
+        <v>0.1096514112116624</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>8049</v>
+        <v>8478</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>晶采</t>
+          <t>東哥遊艇</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>251.0241121846801</v>
+        <v>267.7887244624446</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>24.45</v>
+        <v>140</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>44.08451299593214</v>
+        <v>44.4228761533243</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>14.27682828410773</v>
+        <v>7.523932378013983</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.5238754844087758</v>
+        <v>1.199927762321393</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.0373960928947667</v>
+        <v>0.1314310497029081</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>8047</v>
+        <v>8443</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>星雲</t>
+          <t>阿瘦</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>247.3526021820107</v>
+        <v>265.1967268044963</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>44.5</v>
+        <v>11.15</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>50.27470372235318</v>
+        <v>44.61126930798109</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>8.957065075895995</v>
+        <v>52.49667401250918</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.113023618742389</v>
+        <v>0.9088271535977084</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.7257028829608629</v>
+        <v>0.003717141534968</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>8454</v>
+        <v>8049</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>晶采</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>241.2606117509233</v>
+        <v>251.0241121846801</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>241</v>
+        <v>24.45</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,49 +5587,49 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>47.26365857642308</v>
+        <v>44.08451299593214</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>11.72338521848564</v>
+        <v>14.27682828410773</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.4248457621423513</v>
+        <v>0.5238754844087758</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L97" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M97" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.6324199211364632</v>
+        <v>0.0373960928947667</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>8088</v>
+        <v>8047</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>品安</t>
+          <t>星雲</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>241.1662747808778</v>
+        <v>247.3526021820107</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>43.8</v>
+        <v>44.5</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>49.76560314618668</v>
+        <v>50.27470372235318</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>13.65590901646543</v>
+        <v>8.957065075895995</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1.256252621157641</v>
+        <v>1.113023618742389</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,7 +5658,7 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.3767863554903351</v>
+        <v>0.7257028829608629</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -5668,21 +5668,21 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>8163</v>
+        <v>8454</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>達方</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>240.6094488777084</v>
+        <v>241.2606117509233</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>29.85</v>
+        <v>241</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,49 +5693,49 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>42.87981992314916</v>
+        <v>47.26365857642308</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>12.6283898921754</v>
+        <v>11.72338521848564</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.7551403039045136</v>
+        <v>0.4248457621423513</v>
       </c>
       <c r="K99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L99" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M99" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.07353961685529251</v>
+        <v>0.6324199211364632</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>8101</v>
+        <v>8088</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>品安</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>229.8513971298646</v>
+        <v>241.1662747808778</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>10.3</v>
+        <v>43.8</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>42.34906414883429</v>
+        <v>49.76560314618668</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>16.44365345226704</v>
+        <v>13.65590901646543</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.1301251686168711</v>
+        <v>1.256252621157641</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.1209711912520924</v>
+        <v>0.3767863554903351</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>8222</v>
+        <v>8163</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>寶一</t>
+          <t>達方</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>222.8596613345446</v>
+        <v>240.6094488777084</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>35.1</v>
+        <v>29.85</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>40.73938009094184</v>
+        <v>42.87981992314916</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>8.79481684222638</v>
+        <v>12.6283898921754</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.3870128060262118</v>
+        <v>0.7551403039045136</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.1050530017710232</v>
+        <v>0.07353961685529251</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>8341</v>
+        <v>8101</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>華冠</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>219.1407931165736</v>
+        <v>229.8513971298646</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>73.8</v>
+        <v>10.3</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>37.05648657506774</v>
+        <v>42.34906414883429</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>12.61022694312326</v>
+        <v>16.44365345226704</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.7273447076327048</v>
+        <v>0.1301251686168711</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.029876980103937</v>
+        <v>-0.1209711912520924</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>8429</v>
+        <v>8222</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>金麗-KY</t>
+          <t>寶一</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>216.9587438241342</v>
+        <v>222.8596613345446</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>5.9</v>
+        <v>35.1</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>43.58420405043517</v>
+        <v>40.73938009094184</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>7.421168279513759</v>
+        <v>8.79481684222638</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.4531701565060215</v>
+        <v>0.3870128060262118</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.005698230775918</v>
+        <v>0.1050530017710232</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>8481</v>
+        <v>8341</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>政伸</t>
+          <t>日友</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>215.5256206284074</v>
+        <v>219.1407931165736</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>40.6</v>
+        <v>73.8</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>44.76596797719962</v>
+        <v>37.05648657506774</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>12.1608071468484</v>
+        <v>12.61022694312326</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.3809097872785837</v>
+        <v>0.7273447076327048</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.0491573663829944</v>
+        <v>-0.029876980103937</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -5986,21 +5986,21 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>8367</v>
+        <v>8429</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>建新國際</t>
+          <t>金麗-KY</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>214.9278119846296</v>
+        <v>216.9587438241342</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>40.9</v>
+        <v>5.9</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>53.92689334659694</v>
+        <v>43.58420405043517</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>14.43765889412709</v>
+        <v>7.421168279513759</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>1.045493223751115</v>
+        <v>0.4531701565060215</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.0423349823476202</v>
+        <v>0.005698230775918</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>8249</v>
+        <v>8481</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>菱光</t>
+          <t>政伸</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>207.2533452155243</v>
+        <v>215.5256206284074</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>39.3</v>
+        <v>40.6</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>46.43233050633585</v>
+        <v>44.76596797719962</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>15.45636345813229</v>
+        <v>12.1608071468484</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.3948254321441044</v>
+        <v>0.3809097872785837</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.1830199942334583</v>
+        <v>-0.0491573663829944</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>8472</v>
+        <v>8367</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>夠麻吉</t>
+          <t>建新國際</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>206.9159547138248</v>
+        <v>214.9278119846296</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>67.90000000000001</v>
+        <v>40.9</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>40.30402073533084</v>
+        <v>53.92689334659694</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>27.99119920105399</v>
+        <v>14.43765889412709</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.0915954713824829</v>
+        <v>1.045493223751115</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-1.15845807655587</v>
+        <v>0.0423349823476202</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>8374</v>
+        <v>8249</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>羅昇</t>
+          <t>菱光</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>183.6479593256479</v>
+        <v>207.2533452155243</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>74.09999999999999</v>
+        <v>39.3</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>36.58205565005205</v>
+        <v>46.43233050633585</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>10.15759231702086</v>
+        <v>15.45636345813229</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>1.391547480317337</v>
+        <v>0.3948254321441044</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.0670311014749827</v>
+        <v>0.1830199942334583</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>9136</v>
+        <v>8472</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>巨騰-DR</t>
+          <t>夠麻吉</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>177.8010407732407</v>
+        <v>206.9159547138248</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>9.199999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>32.33699037530904</v>
+        <v>40.30402073533084</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>17.03304013043113</v>
+        <v>27.99119920105399</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.7136039970620186</v>
+        <v>0.0915954713824829</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.0623463217892638</v>
+        <v>-1.15845807655587</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>8044</v>
+        <v>8374</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>網家</t>
+          <t>羅昇</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>177.1272120300521</v>
+        <v>183.6479593256479</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>24.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>50.00508989235949</v>
+        <v>36.58205565005205</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>17.16102169162326</v>
+        <v>10.15759231702086</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.5176419555989005</v>
+        <v>1.391547480317337</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.1096968622204609</v>
+        <v>-0.0670311014749827</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6304,21 +6304,21 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>8390</v>
+        <v>9136</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>金益鼎</t>
+          <t>巨騰-DR</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>146.0612632875095</v>
+        <v>177.8010407732407</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>90.90000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>43.10246644545018</v>
+        <v>32.33699037530904</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>19.73462802626165</v>
+        <v>17.03304013043113</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.9333942982762388</v>
+        <v>0.7136039970620186</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.2998225699010921</v>
+        <v>0.0623463217892638</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>8487</v>
+        <v>8044</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>愛爾達-創</t>
+          <t>網家</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>145.8629940830281</v>
+        <v>177.1272120300521</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>70.09999999999999</v>
+        <v>24.2</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>42.90424339535345</v>
+        <v>50.00508989235949</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>11.69162783546806</v>
+        <v>17.16102169162326</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.4024438372040744</v>
+        <v>0.5176419555989005</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.0160860633166056</v>
+        <v>0.1096968622204609</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6410,21 +6410,21 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>8067</v>
+        <v>8390</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>志旭</t>
+          <t>金益鼎</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>144.8572864131397</v>
+        <v>146.0612632875095</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>11.5</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>44.57729103507442</v>
+        <v>43.10246644545018</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>17.10783972056232</v>
+        <v>19.73462802626165</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.0983745110757316</v>
+        <v>0.9333942982762388</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,62 +6453,168 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.0373666358650294</v>
+        <v>0.2998225699010921</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
+        <v>8487</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>愛爾達-創</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>145.8629940830281</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>42.90424339535345</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>11.69162783546806</v>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>0.4024438372040744</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N114" s="2" t="n">
+        <v>0.0160860633166056</v>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>8067</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>志旭</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>144.8572864131397</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>44.57729103507442</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>17.10783972056232</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>0.0983745110757316</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>-0.0373666358650294</v>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
         <v>8291</v>
       </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>尚茂</t>
         </is>
       </c>
-      <c r="C114" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D114" s="2" t="n">
+      <c r="C116" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D116" s="2" t="n">
         <v>101.7225705293791</v>
       </c>
-      <c r="E114" s="2" t="n">
+      <c r="E116" s="2" t="n">
         <v>27.3</v>
       </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H114" s="2" t="n">
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2" t="n">
         <v>36.37939091386696</v>
       </c>
-      <c r="I114" s="2" t="n">
+      <c r="I116" s="2" t="n">
         <v>5.328014816327801</v>
       </c>
-      <c r="J114" s="2" t="n">
+      <c r="J116" s="2" t="n">
         <v>0.4352871123868269</v>
       </c>
-      <c r="K114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M114" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N114" s="2" t="n">
+      <c r="K116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N116" s="2" t="n">
         <v>0.0430417503419926</v>
       </c>
-      <c r="O114" s="2" t="inlineStr">
+      <c r="O116" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>

--- a/output/full_scan/batch_seq0_2026-10-08.xlsx
+++ b/output/full_scan/batch_seq0_2026-10-08.xlsx
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>68.75088630194595</v>
+        <v>68.75088632935142</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>28.10480802837484</v>
+        <v>28.10480798345204</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>3.116797984523913</v>
@@ -570,7 +570,7 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>2.32366342052393</v>
+        <v>2.323663420511919</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -605,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>78.06529998048428</v>
+        <v>78.06529995721188</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>29.723726801686</v>
+        <v>29.72372678699149</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>6.348785304834501</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>81.79201383293488</v>
+        <v>81.79201376531975</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>26.23343329350317</v>
+        <v>26.23343334335112</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>5.050581260309642</v>
@@ -676,7 +676,7 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>4.596009139551478</v>
+        <v>4.596009139912002</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1086.834794706046</v>
+        <v>1086.834794706047</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>48.6</v>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>68.88225610974031</v>
+        <v>68.8822564367064</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>12.71477370009238</v>
+        <v>12.71477395958657</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>6.053438558221076</v>
@@ -729,7 +729,7 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1809120752235085</v>
+        <v>0.1809120743822979</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>58.45018457873667</v>
+        <v>58.4501845823948</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>20.14320843718718</v>
+        <v>20.14320835786843</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>2.708240513887385</v>
@@ -782,7 +782,7 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>2.546725260635307</v>
+        <v>2.54672526120009</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>65.49247125176757</v>
+        <v>65.49247102716717</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>29.36609422556742</v>
+        <v>29.36609443169234</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>3.527633586080116</v>
@@ -835,7 +835,7 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1320563081430936</v>
+        <v>0.1320563083834411</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>76.84938281567884</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>31.90821670864898</v>
+        <v>31.90821666487004</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>3.499430075610211</v>
@@ -888,7 +888,7 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>1.690171765293938</v>
+        <v>1.690171765329985</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>62.63600458498946</v>
+        <v>62.63600467842114</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>15.35174302150767</v>
+        <v>15.35174304901884</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>1.11718406970062</v>
@@ -941,7 +941,7 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.2909560719683808</v>
+        <v>0.2909560719082958</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>913.4823175947614</v>
+        <v>913.482317594761</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>21.4</v>
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>68.18608195405631</v>
+        <v>68.18608204862969</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>20.83721276025852</v>
+        <v>20.83721268226257</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>2.057571107754822</v>
@@ -994,7 +994,7 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.1903219129909951</v>
+        <v>0.1903219129188931</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1029,10 +1029,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>70.13349679223855</v>
+        <v>70.13349677324454</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>28.70745281351844</v>
+        <v>28.70745277612681</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>0.4778863829004696</v>
@@ -1047,7 +1047,7 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>34.04661907863557</v>
+        <v>34.04661908188027</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>72.94163909775374</v>
+        <v>72.94163908530838</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>41.41361485522605</v>
+        <v>41.41361492438251</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>0.6692625531607514</v>
@@ -1100,7 +1100,7 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>2.775680817539896</v>
+        <v>2.775680817479805</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>63.96691404230935</v>
+        <v>63.96691405570155</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>25.18102129205635</v>
+        <v>25.18102130560897</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>1.963357044455915</v>
@@ -1188,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>81.41370497450623</v>
+        <v>81.41370495364987</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>19.53505082383182</v>
+        <v>19.53505080478708</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>6.473611031608359</v>
@@ -1206,7 +1206,7 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.08059675246788819</v>
+        <v>0.0805967524654842</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>59.49662286232611</v>
+        <v>59.49662284323976</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>14.91323117272427</v>
+        <v>14.91323119687558</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>1.534705958997361</v>
@@ -1259,7 +1259,7 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>1.816588389102366</v>
+        <v>1.816588389186494</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1294,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>62.4388972160024</v>
+        <v>62.43889721303237</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>23.22194564865272</v>
+        <v>23.22194581142398</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>2.458606094843628</v>
@@ -1312,7 +1312,7 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.3632003323340169</v>
+        <v>0.3632003322859474</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>70.71997515412083</v>
+        <v>70.71997506794207</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>40.20627999984774</v>
+        <v>40.20627998076891</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>1.046727163758227</v>
@@ -1365,7 +1365,7 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>1.493546111939554</v>
+        <v>1.493546112083774</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>67.49986155495134</v>
+        <v>67.49986120007276</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>21.69462928795212</v>
+        <v>21.69462928795211</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>0.7143601124408506</v>
@@ -1418,7 +1418,7 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.07590837969097181</v>
+        <v>0.07590837967895631</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>777.3658025572961</v>
+        <v>777.3658025572965</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>36.2</v>
@@ -1453,10 +1453,10 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>65.64095183501165</v>
+        <v>65.64095171659555</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>31.89755916350121</v>
+        <v>31.8975591871857</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>2.945092476757206</v>
@@ -1471,7 +1471,7 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.3817856753405028</v>
+        <v>0.3817856754366376</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1506,10 +1506,10 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>64.16993954706138</v>
+        <v>64.16993955877308</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>20.51075583973391</v>
+        <v>20.51075586539794</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>2.027136419647595</v>
@@ -1524,7 +1524,7 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.0028493324347198</v>
+        <v>0.0028493324467369</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>722.0710344939591</v>
+        <v>722.0710344939585</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>57.1</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>61.87037167701789</v>
+        <v>61.87037084885841</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>23.26564229588845</v>
+        <v>23.26564275524422</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>0.7971046390887576</v>
@@ -1577,7 +1577,7 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.4582647886122225</v>
+        <v>0.4582647914963733</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1612,10 +1612,10 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>54.63505011888225</v>
+        <v>54.63505010454895</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>5.317508232370102</v>
+        <v>5.317508223301607</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>5.555703376526621</v>
@@ -1630,7 +1630,7 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.1002464076301624</v>
+        <v>0.1002464075868999</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1665,10 +1665,10 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>59.57192608557797</v>
+        <v>59.571926042572</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>15.09701592889266</v>
+        <v>15.09701590845029</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>0.903903555197908</v>
@@ -1683,7 +1683,7 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>1.633715834449046</v>
+        <v>1.633715834208718</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>655.4345781659791</v>
+        <v>655.4345781659807</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>230</v>
@@ -1771,10 +1771,10 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>57.41382261893338</v>
+        <v>57.41382265442704</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>21.01761265133142</v>
+        <v>21.01761279270637</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>0.6416039055495474</v>
@@ -1789,7 +1789,7 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>2.612266514993742</v>
+        <v>2.612266514513069</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>653.8829524402263</v>
+        <v>653.8829524402289</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>68</v>
@@ -1824,10 +1824,10 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>68.28773730178901</v>
+        <v>68.28773726678004</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>15.8947929021889</v>
+        <v>15.89479301723955</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>2.922459904062402</v>
@@ -1842,7 +1842,7 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.863253676281051</v>
+        <v>0.8632536763050837</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>55.20473590781823</v>
+        <v>55.20473590534355</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>37.57523380679167</v>
+        <v>37.57523387915548</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>0.2622878238583767</v>
@@ -1895,7 +1895,7 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.0543360403054329</v>
+        <v>-0.0543360406659547</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>619.9120315310141</v>
+        <v>619.9120315310139</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>2060</v>
@@ -1930,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>47.78381090987602</v>
+        <v>47.78381090353461</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>12.5987322285307</v>
+        <v>12.59873225512207</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>0.6813679857092976</v>
@@ -1948,7 +1948,7 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-6.808955191873824</v>
+        <v>-6.808955194037194</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>612.5266647546071</v>
+        <v>612.5266647546072</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>85.09999999999999</v>
@@ -1983,10 +1983,10 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>49.11929440422172</v>
+        <v>49.11929424679327</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>19.00406645416426</v>
+        <v>19.00406643453842</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>2.064014355832512</v>
@@ -2001,7 +2001,7 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.3928557141328472</v>
+        <v>0.3928557145053897</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>54.47009015855016</v>
+        <v>54.47009007980888</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>38.52500912334865</v>
+        <v>38.52500915954474</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>0.2039126708344463</v>
@@ -2054,7 +2054,7 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.0536524989102179</v>
+        <v>-0.0536524987660113</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>592.9609450057658</v>
+        <v>592.9609450057661</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>50.1</v>
@@ -2089,10 +2089,10 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>55.83982313956914</v>
+        <v>55.83982066102502</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>4.15883751812657</v>
+        <v>4.15883533012968</v>
       </c>
       <c r="J31" s="2" t="n">
         <v>0.3131403187712136</v>
@@ -2107,7 +2107,7 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.1419729024590614</v>
+        <v>0.1419729164712351</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2142,10 +2142,10 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>55.07556762034065</v>
+        <v>55.07556764206406</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>23.30970629242927</v>
+        <v>23.3097062805568</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>0.1556558365170188</v>
@@ -2160,7 +2160,7 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.8245204238784813</v>
+        <v>-0.8245204240106787</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>580.6920907104044</v>
+        <v>580.6920907104042</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>19.4</v>
@@ -2195,7 +2195,7 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>58.98850584969143</v>
+        <v>58.9885059851096</v>
       </c>
       <c r="I33" s="2" t="n">
         <v>28.8338775140695</v>
@@ -2213,7 +2213,7 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.0367323419004866</v>
+        <v>0.0367323414678635</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>573.2361473756329</v>
+        <v>573.236147375629</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>56.5</v>
@@ -2248,10 +2248,10 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>58.74807538178406</v>
+        <v>58.74807517470344</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>22.86551436745738</v>
+        <v>22.86551444506559</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>1.108350446873547</v>
@@ -2266,7 +2266,7 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.9196934811197246</v>
+        <v>0.9196934815523486</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>561.6707711957353</v>
+        <v>561.6707711957355</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>326.5</v>
@@ -2301,10 +2301,10 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>48.75616725156184</v>
+        <v>48.75616715356639</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>12.04954635460285</v>
+        <v>12.04954637506356</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>0.6845297377637236</v>
@@ -2319,7 +2319,7 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.2254880767101654</v>
+        <v>0.2254880780320625</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>53.37589158422116</v>
+        <v>53.37589158890111</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>19.95622744640882</v>
+        <v>19.95622732282192</v>
       </c>
       <c r="J36" s="2" t="n">
         <v>1.06436812333298</v>
@@ -2372,7 +2372,7 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.0257830548826195</v>
+        <v>0.0257830548585841</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2407,10 +2407,10 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>53.29672523006876</v>
+        <v>53.29672523712533</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>27.9068990583525</v>
+        <v>27.90689904747592</v>
       </c>
       <c r="J37" s="2" t="n">
         <v>0.5209096159834906</v>
@@ -2425,7 +2425,7 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.2432142382569972</v>
+        <v>0.2432142382810365</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2460,10 +2460,10 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>47.11262062905258</v>
+        <v>47.11262082691759</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>10.34898960042178</v>
+        <v>10.34898965396156</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>0.6407564156104073</v>
@@ -2478,7 +2478,7 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-0.717665441127562</v>
+        <v>-0.717665445814303</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>54.59729309788906</v>
+        <v>54.59729306043662</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>28.0369515793599</v>
+        <v>28.03695161010849</v>
       </c>
       <c r="J39" s="2" t="n">
         <v>0.3314914356505022</v>
@@ -2531,7 +2531,7 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.1768901601868906</v>
+        <v>-0.1768901602109416</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2566,10 +2566,10 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>57.70629572668711</v>
+        <v>57.70629571501454</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>28.15750577498932</v>
+        <v>28.15750578982357</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>0.4782481924665126</v>
@@ -2584,7 +2584,7 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.1912227348127948</v>
+        <v>0.1912227348368318</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>64.76987253322193</v>
+        <v>64.76987249929114</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>32.53685413188181</v>
+        <v>32.53685407189788</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>0.5670663761275974</v>
@@ -2637,7 +2637,7 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.7175200451707395</v>
+        <v>0.7175200454471335</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>65.40637199469262</v>
+        <v>65.40637205357568</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>49.07272363073445</v>
+        <v>49.07272371017118</v>
       </c>
       <c r="J42" s="2" t="n">
         <v>0.3507565649380665</v>
@@ -2690,7 +2690,7 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>1.505232419359622</v>
+        <v>1.505232417436822</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2725,10 +2725,10 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>52.38533300237361</v>
+        <v>52.38533302618228</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>27.28451893778002</v>
+        <v>27.2845189981397</v>
       </c>
       <c r="J43" s="2" t="n">
         <v>0.5146268722717706</v>
@@ -2764,7 +2764,7 @@
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>515.1378922641563</v>
+        <v>515.1378922641555</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>24.1</v>
@@ -2778,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>56.830794914371</v>
+        <v>56.83079497262705</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>13.91453306425982</v>
+        <v>13.91453302973803</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>2.392350724340234</v>
@@ -2796,7 +2796,7 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.1424846873738943</v>
+        <v>0.1424846873378411</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>54.20933332074446</v>
+        <v>54.20933331408137</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>12.78522607080232</v>
+        <v>12.78522607362251</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>1.171671703038444</v>
@@ -2849,7 +2849,7 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.220507016725546</v>
+        <v>0.2205070166637593</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2884,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>47.65076332000302</v>
+        <v>47.65076339807766</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>34.00702985134878</v>
+        <v>34.00702979493215</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>0.3792983774624572</v>
@@ -2902,7 +2902,7 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-1.895591269792043</v>
+        <v>-1.895591270203962</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2937,10 +2937,10 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>47.42181609444074</v>
+        <v>47.42181613151857</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>30.8976432166122</v>
+        <v>30.89764327166268</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>0.8821235310731542</v>
@@ -2955,7 +2955,7 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.8736886222309268</v>
+        <v>-0.8736886222068998</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>461.0112710596544</v>
+        <v>461.0112710596541</v>
       </c>
       <c r="E48" s="2" t="n">
         <v>81</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>40.58445084506695</v>
+        <v>40.58445097475696</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>22.48321764170405</v>
+        <v>22.48321767797798</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>0.5953315198623444</v>
@@ -3008,7 +3008,7 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.3258135906609768</v>
+        <v>-0.3258135916223669</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>460.538957417092</v>
+        <v>460.5389574170919</v>
       </c>
       <c r="E49" s="2" t="n">
         <v>63.4</v>
@@ -3043,10 +3043,10 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>49.26418390999588</v>
+        <v>49.26418322709255</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>17.75820008719286</v>
+        <v>17.75820020223334</v>
       </c>
       <c r="J49" s="2" t="n">
         <v>1.565331861728069</v>
@@ -3061,7 +3061,7 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.2312142095599967</v>
+        <v>0.2312142104011996</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -3096,10 +3096,10 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>51.24182341014726</v>
+        <v>51.24182343523906</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>7.409446058844591</v>
+        <v>7.409446110866228</v>
       </c>
       <c r="J50" s="2" t="n">
         <v>0.4348522983750438</v>
@@ -3114,7 +3114,7 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.8011644501649202</v>
+        <v>0.8011644496842392</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>47.85265698818198</v>
+        <v>47.8526557618142</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>16.90142867001112</v>
+        <v>16.90142896027152</v>
       </c>
       <c r="J51" s="2" t="n">
         <v>1.207241727081338</v>
@@ -3167,7 +3167,7 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.4152180221018553</v>
+        <v>0.4152180272507331</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
@@ -3202,10 +3202,10 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>51.09471769887392</v>
+        <v>51.09471769204582</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>5.215468956324937</v>
+        <v>5.21546913308271</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>1.061167350748045</v>
@@ -3220,7 +3220,7 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>1.315487352717326</v>
+        <v>1.315487353270122</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>453.378734983228</v>
+        <v>453.3787349832285</v>
       </c>
       <c r="E53" s="2" t="n">
         <v>26.45</v>
@@ -3255,10 +3255,10 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>19.97018239934931</v>
+        <v>19.9701826039015</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>49.04285851443795</v>
+        <v>49.04285846742758</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>1.606984700735965</v>
@@ -3273,7 +3273,7 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.1275823386673414</v>
+        <v>-0.1275823389557558</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>447.0431000301944</v>
+        <v>447.0431000301941</v>
       </c>
       <c r="E54" s="2" t="n">
         <v>34.4</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>65.5662966628927</v>
+        <v>65.56629660445458</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>33.14428458119747</v>
+        <v>33.14428463553833</v>
       </c>
       <c r="J54" s="2" t="n">
         <v>2.228843037556953</v>
@@ -3326,7 +3326,7 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.6710381744245847</v>
+        <v>0.6710381746769489</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>439.2716921379535</v>
+        <v>439.2716921379541</v>
       </c>
       <c r="E55" s="2" t="n">
         <v>50.5</v>
@@ -3361,10 +3361,10 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>51.64396867004989</v>
+        <v>51.64396872143281</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>17.95076643234812</v>
+        <v>17.9507664993572</v>
       </c>
       <c r="J55" s="2" t="n">
         <v>1.261462616369482</v>
@@ -3379,7 +3379,7 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.1092348924513225</v>
+        <v>0.1092348924753506</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -3414,10 +3414,10 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>53.70635728600141</v>
+        <v>53.70635721462754</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>18.66799548297174</v>
+        <v>18.66799556380727</v>
       </c>
       <c r="J56" s="2" t="n">
         <v>0.7225547931200471</v>
@@ -3432,7 +3432,7 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.4690026349035413</v>
+        <v>0.469002634975646</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>60.25695172624757</v>
+        <v>60.2569514491917</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>27.2311602706</v>
+        <v>27.23115991647269</v>
       </c>
       <c r="J57" s="2" t="n">
         <v>0.24034330025339</v>
@@ -3520,10 +3520,10 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>48.05622873834169</v>
+        <v>48.056229116221</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>36.87661600599267</v>
+        <v>36.87661603234269</v>
       </c>
       <c r="J58" s="2" t="n">
         <v>0.4191745087014877</v>
@@ -3538,7 +3538,7 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.0617997258459984</v>
+        <v>-0.0617997259301209</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>414.2031695476912</v>
+        <v>414.2031695476913</v>
       </c>
       <c r="E59" s="2" t="n">
         <v>139</v>
@@ -3573,10 +3573,10 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>52.08418875083346</v>
+        <v>52.0841887599181</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>31.04128221608954</v>
+        <v>31.04128230463137</v>
       </c>
       <c r="J59" s="2" t="n">
         <v>0.432183151738959</v>
@@ -3591,7 +3591,7 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.2512553510402679</v>
+        <v>-0.2512553515209683</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>410.3640017409354</v>
+        <v>410.3640017409241</v>
       </c>
       <c r="E60" s="2" t="n">
         <v>30.95</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>48.57514128544108</v>
+        <v>48.57514081278838</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>16.00618360180705</v>
+        <v>16.00618376690014</v>
       </c>
       <c r="J60" s="2" t="n">
         <v>0.6734366827199414</v>
@@ -3644,7 +3644,7 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.082402606448088</v>
+        <v>0.08240260685667571</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>41.87255004124982</v>
+        <v>41.87255004680194</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>31.70957464210655</v>
+        <v>31.70957463374383</v>
       </c>
       <c r="J61" s="2" t="n">
         <v>0.5161376373223423</v>
@@ -3697,7 +3697,7 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>1.538462846434086</v>
+        <v>1.53846284616971</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>403.2234296852506</v>
+        <v>403.2234296852505</v>
       </c>
       <c r="E62" s="2" t="n">
         <v>12.75</v>
@@ -3732,10 +3732,10 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>51.66410364899698</v>
+        <v>51.66410372268134</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>13.64569296770591</v>
+        <v>13.64569291512223</v>
       </c>
       <c r="J62" s="2" t="n">
         <v>3.650182642688881</v>
@@ -3750,7 +3750,7 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.016754974943874</v>
+        <v>-0.0167549750039606</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>78.68008853777276</v>
+        <v>78.68008848440415</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>37.30805682429794</v>
+        <v>37.30805683877528</v>
       </c>
       <c r="J63" s="2" t="n">
         <v>0.1808425508974529</v>
@@ -3803,7 +3803,7 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.1343239081888085</v>
+        <v>0.1343239082052847</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -3838,10 +3838,10 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>44.94763305541719</v>
+        <v>44.94763311007497</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>20.60234961324448</v>
+        <v>20.60234959844772</v>
       </c>
       <c r="J64" s="2" t="n">
         <v>0.6610502872841946</v>
@@ -3856,7 +3856,7 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.0228012556361702</v>
+        <v>-0.0228012556481884</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>44.64499201724888</v>
+        <v>44.64499184255664</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>21.39136576494574</v>
+        <v>21.39136585885247</v>
       </c>
       <c r="J65" s="2" t="n">
         <v>0.5692080331342624</v>
@@ -3909,7 +3909,7 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.3123991656391873</v>
+        <v>0.3123991659035714</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>395.8634049635209</v>
+        <v>395.8634049635208</v>
       </c>
       <c r="E66" s="2" t="n">
         <v>28.2</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>44.90268834399803</v>
+        <v>44.90268837163893</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>19.1453761405531</v>
+        <v>19.14537615931564</v>
       </c>
       <c r="J66" s="2" t="n">
         <v>1.870816255095116</v>
@@ -3962,7 +3962,7 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.068620610797997</v>
+        <v>0.0686206105644962</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -3997,10 +3997,10 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>42.30937054187002</v>
+        <v>42.30937040162757</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>18.9829820197608</v>
+        <v>18.98298206091577</v>
       </c>
       <c r="J67" s="2" t="n">
         <v>0.9402414291795336</v>
@@ -4015,7 +4015,7 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>5.455581065764903</v>
+        <v>5.455581070812102</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>385.4744141746589</v>
+        <v>385.4744141746588</v>
       </c>
       <c r="E69" s="2" t="n">
         <v>253.5</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>50.85390714794104</v>
+        <v>50.85390712685061</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>8.51251650267225</v>
+        <v>8.512516585072612</v>
       </c>
       <c r="J69" s="2" t="n">
         <v>0.3401844706912896</v>
@@ -4121,7 +4121,7 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>2.469308960224295</v>
+        <v>2.469308965872451</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>381.883635821929</v>
+        <v>381.8836358219291</v>
       </c>
       <c r="E70" s="2" t="n">
         <v>20.1</v>
@@ -4156,10 +4156,10 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>48.47937300937726</v>
+        <v>48.47937261553872</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>18.189632038254</v>
+        <v>18.18963212281596</v>
       </c>
       <c r="J70" s="2" t="n">
         <v>0.5895896159336576</v>
@@ -4174,7 +4174,7 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.0076392896313175</v>
+        <v>-0.0076392895351783</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
@@ -4209,10 +4209,10 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>37.31450991342541</v>
+        <v>37.31451002180922</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>32.27104997860098</v>
+        <v>32.271049915539</v>
       </c>
       <c r="J71" s="2" t="n">
         <v>2.027341329392833</v>
@@ -4227,7 +4227,7 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.06564547922579141</v>
+        <v>-0.065645479466132</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>40.36133842359701</v>
+        <v>40.36133823499912</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>27.1671622292828</v>
+        <v>27.16716222928279</v>
       </c>
       <c r="J72" s="2" t="n">
         <v>0.5989563875292683</v>
@@ -4280,7 +4280,7 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>1.113482669414593</v>
+        <v>1.11348267037599</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>363.8756244375477</v>
+        <v>363.8756244375475</v>
       </c>
       <c r="E73" s="2" t="n">
         <v>13.5</v>
@@ -4315,10 +4315,10 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>28.91138071499005</v>
+        <v>28.91138077834961</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>27.43463926876743</v>
+        <v>27.43463923083703</v>
       </c>
       <c r="J73" s="2" t="n">
         <v>3.017999211374759</v>
@@ -4333,7 +4333,7 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.07199120157396439</v>
+        <v>-0.07199120153791259</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -4368,10 +4368,10 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>8.186849530617351</v>
+        <v>8.186849521093947</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>38.91875935043327</v>
+        <v>38.91875934096507</v>
       </c>
       <c r="J74" s="2" t="n">
         <v>0</v>
@@ -4386,7 +4386,7 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.6442186113205489</v>
+        <v>-0.6442186113085318</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>342.2541318927333</v>
+        <v>342.2541318927296</v>
       </c>
       <c r="E75" s="2" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>37.93765132727655</v>
+        <v>37.93765132163702</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>10.29191459269391</v>
+        <v>10.29191463382808</v>
       </c>
       <c r="J75" s="2" t="n">
         <v>0.1481788815458021</v>
@@ -4474,10 +4474,10 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>46.36827816468684</v>
+        <v>46.36827808779955</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>19.82358684480572</v>
+        <v>19.82358680549904</v>
       </c>
       <c r="J76" s="2" t="n">
         <v>0.6231276079596844</v>
@@ -4492,7 +4492,7 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.08094866985133729</v>
+        <v>0.0809486699085481</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
@@ -4527,10 +4527,10 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>47.36883121178813</v>
+        <v>47.36883116445309</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>25.76774569806857</v>
+        <v>25.76774563302967</v>
       </c>
       <c r="J77" s="2" t="n">
         <v>0.4300255712662324</v>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>54.4546393564756</v>
+        <v>54.45463913456012</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>12.93439385840971</v>
+        <v>12.93439384546284</v>
       </c>
       <c r="J78" s="2" t="n">
         <v>0.8082742977947626</v>
@@ -4598,7 +4598,7 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.3510327509488143</v>
+        <v>0.3510327512252116</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>325.5823637249029</v>
+        <v>325.5823637249026</v>
       </c>
       <c r="E79" s="2" t="n">
         <v>21.4</v>
@@ -4633,10 +4633,10 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>40.96968395903292</v>
+        <v>40.96968346809786</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>21.66693844372921</v>
+        <v>21.66693878677197</v>
       </c>
       <c r="J79" s="2" t="n">
         <v>0.6812827466472959</v>
@@ -4651,7 +4651,7 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.0514943742334104</v>
+        <v>0.0514943744857742</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>320.9511533058237</v>
+        <v>320.9511533058239</v>
       </c>
       <c r="E80" s="2" t="n">
         <v>21.2</v>
@@ -4686,7 +4686,7 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>49.5099278302382</v>
+        <v>49.50992778181669</v>
       </c>
       <c r="I80" s="2" t="n">
         <v>26.70271905232586</v>
@@ -4704,7 +4704,7 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.0085524784235318</v>
+        <v>0.008552478315374</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>42.75933847692557</v>
+        <v>42.75933854615619</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>9.960475002199448</v>
+        <v>9.960474977134094</v>
       </c>
       <c r="J81" s="2" t="n">
         <v>0.6424088091267123</v>
@@ -4757,7 +4757,7 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.07585755166471971</v>
+        <v>0.0758575517248077</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -4792,10 +4792,10 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>28.766054956971</v>
+        <v>28.76605488270419</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>36.71697137807788</v>
+        <v>36.71697133547433</v>
       </c>
       <c r="J82" s="2" t="n">
         <v>2.031379645655545</v>
@@ -4845,10 +4845,10 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>39.32970007741113</v>
+        <v>39.32969969026824</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>24.50740289159818</v>
+        <v>24.50740320759468</v>
       </c>
       <c r="J83" s="2" t="n">
         <v>1.020412423518965</v>
@@ -4863,7 +4863,7 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>1.003513191088885</v>
+        <v>1.003513192290621</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>38.6816204483477</v>
+        <v>38.68162119062995</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>17.61005385355298</v>
+        <v>17.61005387047974</v>
       </c>
       <c r="J84" s="2" t="n">
         <v>0.4077260477119798</v>
@@ -4916,7 +4916,7 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.0648332523656605</v>
+        <v>0.0648332521253112</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
@@ -4951,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>48.61898133368651</v>
+        <v>48.61898132519884</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>17.15197553124404</v>
+        <v>17.15197557328655</v>
       </c>
       <c r="J85" s="2" t="n">
         <v>1.284509031381192</v>
@@ -4969,7 +4969,7 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>2.359339893073635</v>
+        <v>2.359339893049577</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>304.6597532183896</v>
+        <v>304.6597532183895</v>
       </c>
       <c r="E86" s="2" t="n">
         <v>22.85</v>
@@ -5004,10 +5004,10 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>48.18101952296635</v>
+        <v>48.18101951905166</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>5.134452547981376</v>
+        <v>5.134452575093118</v>
       </c>
       <c r="J86" s="2" t="n">
         <v>0.4527522101787211</v>
@@ -5022,7 +5022,7 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.0670511741577253</v>
+        <v>0.0670511741817592</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>50.03724842008068</v>
+        <v>50.03724835491892</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>34.28269015400027</v>
+        <v>34.28269027645776</v>
       </c>
       <c r="J87" s="2" t="n">
         <v>0.2737855717988168</v>
@@ -5075,7 +5075,7 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.0067302870493656</v>
+        <v>-0.0067302870012957</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
@@ -5110,10 +5110,10 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>44.11381566872717</v>
+        <v>44.11381641374432</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>7.975003476572353</v>
+        <v>7.975003368264433</v>
       </c>
       <c r="J88" s="2" t="n">
         <v>0.6654817331165166</v>
@@ -5163,10 +5163,10 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>51.69482753190201</v>
+        <v>51.69482809709368</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>32.46331487373325</v>
+        <v>32.46332434370365</v>
       </c>
       <c r="J89" s="2" t="n">
         <v>1.413418222611168</v>
@@ -5181,7 +5181,7 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.1009603142557269</v>
+        <v>0.1009603071775346</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>282.6055382257987</v>
+        <v>282.6055382257988</v>
       </c>
       <c r="E90" s="2" t="n">
         <v>9.65</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>37.30767587746976</v>
+        <v>37.30767331140419</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>26.13846135011506</v>
+        <v>26.13846145517847</v>
       </c>
       <c r="J90" s="2" t="n">
         <v>1.497673942166656</v>
@@ -5234,7 +5234,7 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.0072446634574273</v>
+        <v>-0.0072446632290987</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>279.1479950597467</v>
+        <v>279.1479950597472</v>
       </c>
       <c r="E91" s="2" t="n">
         <v>58.4</v>
@@ -5269,10 +5269,10 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>16.26069884120197</v>
+        <v>16.26069884838886</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>36.15212986199487</v>
+        <v>36.15212981069186</v>
       </c>
       <c r="J91" s="2" t="n">
         <v>1.04537194403018</v>
@@ -5287,7 +5287,7 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.1743288727172258</v>
+        <v>-0.1743288727652986</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>273.5740563964841</v>
+        <v>273.574056396484</v>
       </c>
       <c r="E92" s="2" t="n">
         <v>15.15</v>
@@ -5322,10 +5322,10 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>53.51978085092245</v>
+        <v>53.51978105138596</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>11.42925392938144</v>
+        <v>11.42925411410283</v>
       </c>
       <c r="J92" s="2" t="n">
         <v>0.2729448192959408</v>
@@ -5340,7 +5340,7 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.0484213543037463</v>
+        <v>0.0484213541715555</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>273.1714851159183</v>
+        <v>273.1714851159185</v>
       </c>
       <c r="E93" s="2" t="n">
         <v>199.5</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>39.2441181299348</v>
+        <v>39.24411813866484</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>12.94927338308331</v>
+        <v>12.9492733830833</v>
       </c>
       <c r="J93" s="2" t="n">
         <v>1.020988026920266</v>
@@ -5393,7 +5393,7 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.3233670559437325</v>
+        <v>0.323367055823577</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
@@ -5428,10 +5428,10 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>47.11690506183617</v>
+        <v>47.1169050348886</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>46.49694560027209</v>
+        <v>46.4969456456187</v>
       </c>
       <c r="J94" s="2" t="n">
         <v>1.067541341736764</v>
@@ -5446,7 +5446,7 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.1096514112116624</v>
+        <v>0.1096514111635917</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>267.7887244624446</v>
+        <v>267.7887244624445</v>
       </c>
       <c r="E95" s="2" t="n">
         <v>140</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>44.4228761533243</v>
+        <v>44.42287609493049</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>7.523932378013983</v>
+        <v>7.523932393340924</v>
       </c>
       <c r="J95" s="2" t="n">
         <v>1.199927762321393</v>
@@ -5499,7 +5499,7 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.1314310497029081</v>
+        <v>0.1314310485011802</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>44.61126930798109</v>
+        <v>44.6112693938418</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>52.49667401250918</v>
+        <v>52.49667392345407</v>
       </c>
       <c r="J96" s="2" t="n">
         <v>0.9088271535977084</v>
@@ -5587,10 +5587,10 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>44.08451299593214</v>
+        <v>44.08451311235183</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>14.27682828410773</v>
+        <v>14.27682831659762</v>
       </c>
       <c r="J97" s="2" t="n">
         <v>0.5238754844087758</v>
@@ -5605,7 +5605,7 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.0373960928947667</v>
+        <v>0.037396092858715</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>247.3526021820107</v>
+        <v>247.3526021820109</v>
       </c>
       <c r="E98" s="2" t="n">
         <v>44.5</v>
@@ -5643,7 +5643,7 @@
         <v>50.27470372235318</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>8.957065075895995</v>
+        <v>8.957065137947493</v>
       </c>
       <c r="J98" s="2" t="n">
         <v>1.113023618742389</v>
@@ -5658,7 +5658,7 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.7257028829608629</v>
+        <v>0.725702883008934</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>47.26365857642308</v>
+        <v>47.26365854264361</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>11.72338521848564</v>
+        <v>11.72338522170471</v>
       </c>
       <c r="J99" s="2" t="n">
         <v>0.4248457621423513</v>
@@ -5711,7 +5711,7 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.6324199211364632</v>
+        <v>0.6324199214969837</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -5746,10 +5746,10 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>49.76560314618668</v>
+        <v>49.76560302511928</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>13.65590901646543</v>
+        <v>13.65590902203867</v>
       </c>
       <c r="J100" s="2" t="n">
         <v>1.256252621157641</v>
@@ -5764,7 +5764,7 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.3767863554903351</v>
+        <v>0.3767863556465586</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>240.6094488777084</v>
+        <v>240.6094488777083</v>
       </c>
       <c r="E101" s="2" t="n">
         <v>29.85</v>
@@ -5799,10 +5799,10 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>42.87981992314916</v>
+        <v>42.87981975660852</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>12.6283898921754</v>
+        <v>12.6283900105753</v>
       </c>
       <c r="J101" s="2" t="n">
         <v>0.7551403039045136</v>
@@ -5817,7 +5817,7 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.07353961685529251</v>
+        <v>0.0735396170235324</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>229.8513971298646</v>
+        <v>229.8513971298647</v>
       </c>
       <c r="E102" s="2" t="n">
         <v>10.3</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>42.34906414883429</v>
+        <v>42.34906423635634</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>16.44365345226704</v>
+        <v>16.44365345752313</v>
       </c>
       <c r="J102" s="2" t="n">
         <v>0.1301251686168711</v>
@@ -5870,7 +5870,7 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.1209711912520924</v>
+        <v>-0.1209711913602483</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
@@ -5905,10 +5905,10 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>40.73938009094184</v>
+        <v>40.73937871427032</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>8.79481684222638</v>
+        <v>8.794816886834091</v>
       </c>
       <c r="J103" s="2" t="n">
         <v>0.3870128060262118</v>
@@ -5923,7 +5923,7 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.1050530017710232</v>
+        <v>0.1050530029246817</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -5958,10 +5958,10 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>37.05648657506774</v>
+        <v>37.05648644967242</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>12.61022694312326</v>
+        <v>12.61022695342716</v>
       </c>
       <c r="J104" s="2" t="n">
         <v>0.7273447076327048</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.029876980103937</v>
+        <v>-0.0298769800799026</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>43.58420405043517</v>
+        <v>43.5842038159188</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>7.421168279513759</v>
+        <v>7.421168319736209</v>
       </c>
       <c r="J105" s="2" t="n">
         <v>0.4531701565060215</v>
@@ -6029,7 +6029,7 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.005698230775918</v>
+        <v>0.0056982307807249</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>215.5256206284074</v>
+        <v>215.5256206284072</v>
       </c>
       <c r="E106" s="2" t="n">
         <v>40.6</v>
@@ -6064,10 +6064,10 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>44.76596797719962</v>
+        <v>44.7659681387316</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>12.1608071468484</v>
+        <v>12.16080718526336</v>
       </c>
       <c r="J106" s="2" t="n">
         <v>0.3809097872785837</v>
@@ -6082,7 +6082,7 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.0491573663829944</v>
+        <v>-0.0491573665031703</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>214.9278119846296</v>
+        <v>214.9278119846295</v>
       </c>
       <c r="E107" s="2" t="n">
         <v>40.9</v>
@@ -6117,10 +6117,10 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>53.92689334659694</v>
+        <v>53.92689331764274</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>14.43765889412709</v>
+        <v>14.43765886797527</v>
       </c>
       <c r="J107" s="2" t="n">
         <v>1.045493223751115</v>
@@ -6156,7 +6156,7 @@
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>207.2533452155243</v>
+        <v>207.2533452155261</v>
       </c>
       <c r="E108" s="2" t="n">
         <v>39.3</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>46.43233050633585</v>
+        <v>46.4323300759787</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>15.45636345813229</v>
+        <v>15.45636357093937</v>
       </c>
       <c r="J108" s="2" t="n">
         <v>0.3948254321441044</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.1830199942334583</v>
+        <v>0.1830199946901065</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6223,10 +6223,10 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>40.30402073533084</v>
+        <v>40.30402100914071</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>27.99119920105399</v>
+        <v>27.99119922148739</v>
       </c>
       <c r="J109" s="2" t="n">
         <v>0.0915954713824829</v>
@@ -6241,7 +6241,7 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-1.15845807655587</v>
+        <v>-1.158458077373055</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>183.6479593256479</v>
+        <v>183.647959325648</v>
       </c>
       <c r="E110" s="2" t="n">
         <v>74.09999999999999</v>
@@ -6276,10 +6276,10 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>36.58205565005205</v>
+        <v>36.58205534000025</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>10.15759231702086</v>
+        <v>10.15759242355149</v>
       </c>
       <c r="J110" s="2" t="n">
         <v>1.391547480317337</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.0670311014749827</v>
+        <v>-0.0670311012346347</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>32.33699037530904</v>
+        <v>32.33699024086408</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>17.03304013043113</v>
+        <v>17.03304014948704</v>
       </c>
       <c r="J111" s="2" t="n">
         <v>0.7136039970620186</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.0623463217892638</v>
+        <v>0.0623463218301228</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6382,10 +6382,10 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>50.00508989235949</v>
+        <v>50.00508988237379</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>17.16102169162326</v>
+        <v>17.16102174116885</v>
       </c>
       <c r="J112" s="2" t="n">
         <v>0.5176419555989005</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.1096968622204609</v>
+        <v>0.1096968622444947</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>146.0612632875095</v>
+        <v>146.0612632875094</v>
       </c>
       <c r="E113" s="2" t="n">
         <v>90.90000000000001</v>
@@ -6435,10 +6435,10 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>43.10246644545018</v>
+        <v>43.10246649428943</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>19.73462802626165</v>
+        <v>19.73462790332274</v>
       </c>
       <c r="J113" s="2" t="n">
         <v>0.9333942982762388</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>42.90424339535345</v>
+        <v>42.90424351613235</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>11.69162783546806</v>
+        <v>11.6916278776238</v>
       </c>
       <c r="J114" s="2" t="n">
         <v>0.4024438372040744</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.0160860633166056</v>
+        <v>0.0160860631002954</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>144.8572864131397</v>
+        <v>144.8572864131396</v>
       </c>
       <c r="E115" s="2" t="n">
         <v>11.5</v>
@@ -6541,10 +6541,10 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>44.57729103507442</v>
+        <v>44.57729662833026</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>17.10783972056232</v>
+        <v>17.10783998825587</v>
       </c>
       <c r="J115" s="2" t="n">
         <v>0.0983745110757316</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.0373666358650294</v>
+        <v>-0.0373666390255794</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6594,10 +6594,10 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>36.37939091386696</v>
+        <v>36.37930077741147</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>5.328014816327801</v>
+        <v>5.327904602012652</v>
       </c>
       <c r="J116" s="2" t="n">
         <v>0.4352871123868269</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.0430417503419926</v>
+        <v>0.0430368640187484</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
